--- a/kits/security-questionnaire/samples/library/answer_library_DRAFT.xlsx
+++ b/kits/security-questionnaire/samples/library/answer_library_DRAFT.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Library'!$A$1:$N$96</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Evidence'!$A$1:$H$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Evidence'!$A$1:$H$222</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Documents'!$A$1:$F$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,10 +30,10 @@
   </numFmts>
   <fonts count="4">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -980,9 +980,21 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Incident Response Plan v1.1</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>4. Roles</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Incident Lead: the CTO (backup: the on-call senior engineer). Runs the response and makes technical decisions. • Communications Lead: the CEO. Approves all messages to customers, regulators and partners. • Responders: engineers assigned by the Incident Lead.</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Dana Whitfield, CTO</t>
@@ -992,12 +1004,12 @@
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>NEEDS CLIENT INPUT</t>
+          <t>Draft</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>Documents seem silent. Only a weak match (score 0.08): Access Control Policy v1.3, 3. Principles. Check it on the Evidence sheet, then ask the client.</t>
+          <t>Possible source found automatically (score 0.14). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1156,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>Documents seem silent. Only a weak match (score 0.09): Vendor Management Policy v1.0, 3. Assessment before use. Check it on the Evidence sheet, then ask the client.</t>
+          <t>Documents seem silent. Only a weak match (score 0.09): Access Control Policy v1.3, 2. Scope. Check it on the Evidence sheet, then ask the client.</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1271,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.19). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.16). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1329,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.15). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.16). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.33). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.17). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1682,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Documents seem silent. Only a weak match (score 0.09): Vendor Management Policy v1.0, (whole document). Check it on the Evidence sheet, then ask the client.</t>
+          <t>Documents seem silent. Only a weak match (score 0.10): Vendor Management Policy v1.0, (whole document). Check it on the Evidence sheet, then ask the client.</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1798,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.43). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.44). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1855,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.32). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.31). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1912,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.41). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.34). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1970,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.24). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.22). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2201,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.36). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.38). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2259,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.36). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.38). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -2278,17 +2290,17 @@
       <c r="F27" s="3" t="n"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>2. Data at rest</t>
+          <t>6. Encryption</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Customer data stored in Amazon RDS, Amazon S3 and EBS volumes is encrypted at rest with AES-256 using AWS Key Management Service (KMS). Encryption is on by default for new storage, and a configuration check raises an alert if unencrypted storage is created.</t>
+          <t>All backups and snapshots are encrypted with AES-256 using AWS Key Management Service (KMS) keys.</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2305,7 +2317,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.26). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.27). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2376,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.36). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.35). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2434,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.37). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.38). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2490,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.27). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.28). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2604,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.27). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.28). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2649,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>Documents seem silent. Only a weak match (score 0.09): Vendor Management Policy v1.0, 2. Vendor register. Check it on the Evidence sheet, then ask the client.</t>
+          <t>Documents seem silent. Only a weak match (score 0.09): Vendor Management Policy v1.0, 3. Assessment before use. Check it on the Evidence sheet, then ask the client.</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2707,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.15). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.16). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2752,7 @@
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>Documents seem silent. Only a weak match (score 0.07): Secure Development Policy v1.2, 5. Environments. Check it on the Evidence sheet, then ask the client.</t>
+          <t>Documents seem silent. Only a weak match (score 0.09): Secure Development Policy v1.2, 5. Environments. Check it on the Evidence sheet, then ask the client.</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2810,7 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.16). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.13). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2867,7 @@
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.20). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.21). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2969,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.40). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.39). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3160,7 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.21). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.28). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3216,7 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.52). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.64). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3329,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.31). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.38). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3386,7 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.30). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.29). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3442,7 @@
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.27). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.31). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3613,7 @@
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.46). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.49). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3727,7 @@
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.15). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.16). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3886,7 @@
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.36). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.37). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3944,7 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.36). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.41). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -3988,7 +4000,7 @@
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.38). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.48). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4286,7 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.30). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.31). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4455,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.63). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.66). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4968,7 @@
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.38). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.39). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5128,7 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.27). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.26). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5274,7 @@
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>Possible source found automatically (score 0.21). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
+          <t>Possible source found automatically (score 0.24). Read the section; write an answer only if it really supports one. Other candidates: Evidence sheet.</t>
         </is>
       </c>
     </row>
@@ -5498,7 +5510,7 @@
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>Documents seem silent. Only a weak match (score 0.10): Access Control Policy v1.3, 8. Remote access. Check it on the Evidence sheet, then ask the client.</t>
+          <t>Documents seem silent. Only a weak match (score 0.10): Access Control Policy v1.3, 5.1 Production administrators. Check it on the Evidence sheet, then ask the client.</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5758,7 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>No matching text found in the documents provided. Ask the client (or for a document that covers it).</t>
+          <t>Documents seem silent. Only a weak match (score 0.08): Encryption and Key Management Standard v1.1, 6. Laptops. Check it on the Evidence sheet, then ask the client.</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5891,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>No matching text found in the documents provided. Ask the client (or for a document that covers it).</t>
+          <t>Documents seem silent. Only a weak match (score 0.11): Encryption and Key Management Standard v1.1, 6. Laptops. Check it on the Evidence sheet, then ask the client.</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H213"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6152,7 +6164,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -6226,32 +6238,30 @@
           <t>Who is accountable for information security at the company?</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>1 (weak)</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>3. Principles</t>
+          <t>4. Roles</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Every person has an individual, named account. Shared or generic accounts are not allowed, except the break-glass account described in section 5.3.</t>
+          <t>Incident Lead: the CTO (backup: the on-call senior engineer). Runs the response and makes technical decisions. • Communications Lead: the CEO. Approves all messages to customers, regulators and partners. • Responders: engineers assigned by the Incident Lead.</t>
         </is>
       </c>
     </row>
@@ -6272,64 +6282,66 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>4. Roles</t>
+          <t>3. Principles</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Incident Lead: the CTO (backup: the on-call senior engineer). Runs the response and makes technical decisions.</t>
+          <t>Every person has an individual, named account. Shared or generic accounts are not allowed, except the break-glass account described in section 5.3.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>GOV-003</t>
+          <t>GOV-002</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>How often are security policies reviewed and updated?</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
+          <t>Who is accountable for information security at the company?</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>9. Policy review</t>
+          <t>1. Purpose</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>This policy is reviewed at least annually and after any significant change to systems or the organisation.</t>
+          <t>This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
         </is>
       </c>
     </row>
@@ -6345,29 +6357,29 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>(start of document)</t>
+          <t>9. Policy review</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>FICTIONAL SAMPLE. Quarterhour, Inc. is a made-up company used to demonstrate this kit. • Document ID: QH-POL-09 • Version: 1.0 • Owner: Dana Whitfield, CTO • Approved by: Maya Okafor, CEO • Last reviewed: 20 May 2026 • Review cycle: at least annually</t>
+          <t>This policy is reviewed at least annually and after any significant change to systems or the organisation.</t>
         </is>
       </c>
     </row>
@@ -6383,14 +6395,14 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0.36</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -6400,64 +6412,62 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>FICTIONAL SAMPLE. Quarterhour, Inc. is a made-up company used to demonstrate this kit. • Document ID: QH-POL-11 • Version: 1.2 • Owner: Dana Whitfield, CTO • Approved by: Maya Okafor, CEO • Last reviewed: 8 August 2026 • Review cycle: at least annually</t>
+          <t>FICTIONAL SAMPLE. Quarterhour, Inc. is a made-up company used to demonstrate this kit. • Document ID: QH-POL-09 • Version: 1.0 • Owner: Dana Whitfield, CTO • Approved by: Maya Okafor, CEO • Last reviewed: 20 May 2026 • Review cycle: at least annually</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>GOV-004</t>
+          <t>GOV-003</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Does the company carry out a formal security risk assessment at least once a year?</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>1 (weak)</t>
-        </is>
+          <t>How often are security policies reviewed and updated?</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.1</v>
+        <v>0.36</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>1. Purpose</t>
+          <t>(start of document)</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>To manage the security risk of third parties that store or process Quarterhour or customer data.</t>
+          <t>FICTIONAL SAMPLE. Quarterhour, Inc. is a made-up company used to demonstrate this kit. • Document ID: QH-POL-11 • Version: 1.2 • Owner: Dana Whitfield, CTO • Approved by: Maya Okafor, CEO • Last reviewed: 8 August 2026 • Review cycle: at least annually</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>GOV-005</t>
+          <t>GOV-004</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Do employees and contractors formally acknowledge the security policies?</t>
+          <t>Does the company carry out a formal security risk assessment at least once a year?</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -6466,7 +6476,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -6475,7 +6485,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>3. Assessment before use</t>
+          <t>1. Purpose</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -6485,7 +6495,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Before a new vendor receives customer data: • the contract owner completes a vendor risk review; • for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire; • a data processing agreement is signed if the vendor will process personal data. • The CTO approves every high-risk vendor.</t>
+          <t>To manage the security risk of third parties that store or process Quarterhour or customer data.</t>
         </is>
       </c>
     </row>
@@ -6502,30 +6512,30 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2 (weak)</t>
+          <t>1 (weak)</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>2. Scope</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2. To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
+          <t>It applies to all employees and contractors, and to every system that stores or processes Quarterhour or customer data, including AWS, GitHub, Google Workspace, Stripe and the Quarterhour admin console.</t>
         </is>
       </c>
     </row>
@@ -6542,7 +6552,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -6550,79 +6560,81 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>2. Scope</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>It applies to all employees and contractors, and to every system that stores or processes Quarterhour or customer data, including AWS, GitHub, Google Workspace, Stripe and the Quarterhour admin console.</t>
+          <t>Secure Development Policy v1.2. To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>CMP-001</t>
+          <t>GOV-005</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Does the company have a current SOC 2 Type II report?</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
+          <t>Do employees and contractors formally acknowledge the security policies?</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>3. Assessment before use</t>
+          <t>9. Policy review</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire;</t>
+          <t>This policy is reviewed at least annually and after any significant change to systems or the organisation.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>CMP-002</t>
+          <t>CMP-001</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Is the company certified to ISO/IEC 27001?</t>
+          <t>Does the company have a current SOC 2 Type II report?</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -6648,19 +6660,19 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>CMP-003</t>
+          <t>CMP-002</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>How does the company meet GDPR requirements when it processes personal data of people in the EU or UK?</t>
+          <t>Is the company certified to ISO/IEC 27001?</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -6679,7 +6691,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>Before a new vendor receives customer data: • the contract owner completes a vendor risk review; • for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire; • a data processing agreement is signed if the vendor will process personal data. • The CTO approves every high-risk vendor.</t>
+          <t>for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire;</t>
         </is>
       </c>
     </row>
@@ -6694,13 +6706,11 @@
           <t>How does the company meet GDPR requirements when it processes personal data of people in the EU or UK?</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+      <c r="C17" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -6709,7 +6719,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>4. Contracts</t>
+          <t>3. Assessment before use</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -6719,7 +6729,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Vendor contracts must include confidentiality obligations and security requirements, plus data protection terms where personal data is involved.</t>
+          <t>Before a new vendor receives customer data: • the contract owner completes a vendor risk review; • for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire; • a data processing agreement is signed if the vendor will process personal data. • The CTO approves every high-risk vendor.</t>
         </is>
       </c>
     </row>
@@ -6736,11 +6746,11 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -6749,7 +6759,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>6. Subprocessor changes</t>
+          <t>4. Contracts</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -6759,26 +6769,28 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Customers are told at least 30 days before a new subprocessor starts processing their personal data. Notice is sent by email to customer account administrators and the public subprocessor list is updated.</t>
+          <t>Vendor contracts must include confidentiality obligations and security requirements, plus data protection terms where personal data is involved.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>CMP-004</t>
+          <t>CMP-003</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Does the company store, process or transmit payment card data?</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>1</v>
+          <t>How does the company meet GDPR requirements when it processes personal data of people in the EU or UK?</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -6787,7 +6799,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>7. Key vendors</t>
+          <t>6. Subprocessor changes</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -6797,26 +6809,26 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers.</t>
+          <t>Customers are told at least 30 days before a new subprocessor starts processing their personal data. Notice is sent by email to customer account administrators and the public subprocessor list is updated.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>HR-002</t>
+          <t>CMP-004</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Do all employees and contractors sign confidentiality agreements?</t>
+          <t>Does the company store, process or transmit payment card data?</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -6825,7 +6837,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>4. Contracts</t>
+          <t>7. Key vendors</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -6835,7 +6847,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Vendor contracts must include confidentiality obligations and security requirements, plus data protection terms where personal data is involved.</t>
+          <t>Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers.</t>
         </is>
       </c>
     </row>
@@ -6850,32 +6862,30 @@
           <t>Do all employees and contractors sign confidentiality agreements?</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+      <c r="C21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>2. Scope</t>
+          <t>4. Contracts</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>It applies to all employees and contractors, and to every system that stores or processes Quarterhour or customer data, including AWS, GitHub, Google Workspace, Stripe and the Quarterhour admin console.</t>
+          <t>Vendor contracts must include confidentiality obligations and security requirements, plus data protection terms where personal data is involved.</t>
         </is>
       </c>
     </row>
@@ -6892,108 +6902,110 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>3. Assessment before use</t>
+          <t>2. Scope</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Before a new vendor receives customer data: • the contract owner completes a vendor risk review; • for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire; • a data processing agreement is signed if the vendor will process personal data. • The CTO approves every high-risk vendor.</t>
+          <t>It applies to all employees and contractors, and to every system that stores or processes Quarterhour or customer data, including AWS, GitHub, Google Workspace, Stripe and the Quarterhour admin console.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>HR-003</t>
+          <t>HR-002</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Do all staff complete security awareness training when they join and at least once a year?</t>
+          <t>Do all employees and contractors sign confidentiality agreements?</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>1 (weak)</t>
+          <t>3 (weak)</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>9. Training</t>
+          <t>3. Assessment before use</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Engineers complete secure coding training based on the OWASP Top 10 when they join and every year after that.</t>
+          <t>Before a new vendor receives customer data: • the contract owner completes a vendor risk review; • for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire; • a data processing agreement is signed if the vendor will process personal data. • The CTO approves every high-risk vendor.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>HR-004</t>
+          <t>HR-003</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>How quickly is access removed when an employee or contractor leaves?</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>1</v>
+          <t>Do all staff complete security awareness training when they join and at least once a year?</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>1 (weak)</t>
+        </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.33</v>
+        <v>0.11</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>6. Joiners, movers and leavers</t>
+          <t>9. Training</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>When someone leaves, all access is revoked within 24 hours of their last working day, or on the same day for involuntary departures. Company devices are returned and wiped.</t>
+          <t>Engineers complete secure coding training based on the OWASP Top 10 when they join and every year after that.</t>
         </is>
       </c>
     </row>
@@ -7008,13 +7020,11 @@
           <t>How quickly is access removed when an employee or contractor leaves?</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -7023,7 +7033,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>2. Scope</t>
+          <t>6. Joiners, movers and leavers</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -7033,7 +7043,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>It applies to all employees and contractors, and to every system that stores or processes Quarterhour or customer data, including AWS, GitHub, Google Workspace, Stripe and the Quarterhour admin console.</t>
+          <t>When someone leaves, all access is revoked within 24 hours of their last working day, or on the same day for involuntary departures. Company devices are returned and wiped.</t>
         </is>
       </c>
     </row>
@@ -7050,11 +7060,11 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -7080,17 +7090,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>HR-005</t>
+          <t>HR-004</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Is there a disciplinary process for breaches of security policy?</t>
+          <t>How quickly is access removed when an employee or contractor leaves?</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>1 (weak)</t>
+          <t>3 (weak)</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -7098,22 +7108,22 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>2. Scope</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0. To manage the security risk of third parties that store or process Quarterhour or customer data.</t>
+          <t>It applies to all employees and contractors, and to every system that stores or processes Quarterhour or customer data, including AWS, GitHub, Google Workspace, Stripe and the Quarterhour admin console.</t>
         </is>
       </c>
     </row>
@@ -7130,15 +7140,15 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2 (weak)</t>
+          <t>1 (weak)</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -7148,12 +7158,12 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2. To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
+          <t>Vendor Management Policy v1.0. To manage the security risk of third parties that store or process Quarterhour or customer data.</t>
         </is>
       </c>
     </row>
@@ -7170,49 +7180,51 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>9. Policy review</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>This policy is reviewed at least annually and after any significant change to systems or the organisation.</t>
+          <t>Secure Development Policy v1.2. To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>AC-001</t>
+          <t>HR-005</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Is access to systems and data granted on a least-privilege, role-based basis?</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>1</v>
+          <t>Is there a disciplinary process for breaches of security policy?</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.3</v>
+        <v>0.08</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -7221,7 +7233,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>3. Principles</t>
+          <t>9. Policy review</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -7231,7 +7243,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Access is granted on a least-privilege basis: people get only the access their role needs.</t>
+          <t>This policy is reviewed at least annually and after any significant change to systems or the organisation.</t>
         </is>
       </c>
     </row>
@@ -7246,13 +7258,11 @@
           <t>Is access to systems and data granted on a least-privilege, role-based basis?</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+      <c r="C31" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.08</v>
+        <v>0.3</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -7261,7 +7271,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>6. Joiners, movers and leavers</t>
+          <t>3. Principles</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -7271,7 +7281,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>When someone changes role, access they no longer need is removed within 5 business days.</t>
+          <t>Access is granted on a least-privilege basis: people get only the access their role needs.</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7298,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -7296,60 +7306,62 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>1. Purpose</t>
+          <t>6. Joiners, movers and leavers</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
+          <t>When someone changes role, access they no longer need is removed within 5 business days.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>AC-002</t>
+          <t>AC-001</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Is multi-factor authentication required for all workforce accounts?</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>1</v>
+          <t>Is access to systems and data granted on a least-privilege, role-based basis?</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.43</v>
+        <v>0.08</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Encryption and Key Management Standard v1.1</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>4.2 Multi-factor authentication</t>
+          <t>1. Purpose</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>encryption-standard.docx</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Multi-factor authentication (MFA) is required for all workforce accounts on Google Workspace, AWS, GitHub and Stripe, and on any other system that supports it. Administrators must use a hardware security key or an authenticator app. SMS codes are not allowed for administrator accounts.</t>
+          <t>This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
         </is>
       </c>
     </row>
@@ -7364,32 +7376,30 @@
           <t>Is multi-factor authentication required for all workforce accounts?</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+      <c r="C34" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>7. Key vendors</t>
+          <t>4.2 Multi-factor authentication</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
+          <t>Multi-factor authentication (MFA) is required for all workforce accounts on Google Workspace, AWS, GitHub and Stripe, and on any other system that supports it. Administrators must use a hardware security key or an authenticator app. SMS codes are not allowed for administrator accounts.</t>
         </is>
       </c>
     </row>
@@ -7406,11 +7416,11 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -7436,38 +7446,40 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>AC-003</t>
+          <t>AC-002</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Is multi-factor authentication required for administrator access to production systems?</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>1</v>
+          <t>Is multi-factor authentication required for all workforce accounts?</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.32</v>
+        <v>0.09</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>4.2 Multi-factor authentication</t>
+          <t>7. Key vendors</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Multi-factor authentication (MFA) is required for all workforce accounts on Google Workspace, AWS, GitHub and Stripe, and on any other system that supports it. Administrators must use a hardware security key or an authenticator app. SMS codes are not allowed for administrator accounts.</t>
+          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
         </is>
       </c>
     </row>
@@ -7483,10 +7495,10 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -7495,7 +7507,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>5.1 Production administrators</t>
+          <t>4.2 Multi-factor authentication</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -7505,7 +7517,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Administrator access to the production AWS account is limited to the CTO and two named senior engineers. The current list is kept in the access register.</t>
+          <t>Multi-factor authentication (MFA) is required for all workforce accounts on Google Workspace, AWS, GitHub and Stripe, and on any other system that supports it. Administrators must use a hardware security key or an authenticator app. SMS codes are not allowed for administrator accounts.</t>
         </is>
       </c>
     </row>
@@ -7521,10 +7533,10 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -7533,7 +7545,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>5.3 Root and break-glass accounts</t>
+          <t>5.1 Production administrators</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -7543,26 +7555,26 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>The AWS root user is protected with a hardware security key, has no access keys and is used only for tasks that require it. A break-glass administrator account exists for emergencies. Its credentials are sealed in the password manager, and every use is logged and reviewed by the CTO.</t>
+          <t>Administrator access to the production AWS account is limited to the CTO and two named senior engineers. The current list is kept in the access register.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>AC-004</t>
+          <t>AC-003</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Do staff use single sign-on to access internal business applications?</t>
+          <t>Is multi-factor authentication required for administrator access to production systems?</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.41</v>
+        <v>0.23</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -7571,7 +7583,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>4.1 Single sign-on</t>
+          <t>5.3 Root and break-glass accounts</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -7581,7 +7593,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>Google Workspace is the company identity provider. Internal applications that support single sign-on must use it. A few tools that do not support single sign-on use separate accounts protected as described in 4.2 and 4.3.</t>
+          <t>The AWS root user is protected with a hardware security key, has no access keys and is used only for tasks that require it. A break-glass administrator account exists for emergencies. Its credentials are sealed in the password manager, and every use is logged and reviewed by the CTO.</t>
         </is>
       </c>
     </row>
@@ -7596,32 +7608,30 @@
           <t>Do staff use single sign-on to access internal business applications?</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+      <c r="C40" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.08</v>
+        <v>0.34</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>7. Key vendors</t>
+          <t>4.1 Single sign-on</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
+          <t>Google Workspace is the company identity provider. Internal applications that support single sign-on must use it. A few tools that do not support single sign-on use separate accounts protected as described in 4.2 and 4.3.</t>
         </is>
       </c>
     </row>
@@ -7638,49 +7648,51 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>2. Scope</t>
+          <t>7. Key vendors</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>It applies to all employees and contractors, and to every system that stores or processes Quarterhour or customer data, including AWS, GitHub, Google Workspace, Stripe and the Quarterhour admin console.</t>
+          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>AC-005</t>
+          <t>AC-004</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Does the product support single sign-on (SAML or OIDC) for customer users?</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>1</v>
+          <t>Do staff use single sign-on to access internal business applications?</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>0.24</v>
+        <v>0.09</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -7689,7 +7701,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>4.1 Single sign-on</t>
+          <t>2. Scope</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -7699,26 +7711,26 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Google Workspace is the company identity provider. Internal applications that support single sign-on must use it. A few tools that do not support single sign-on use separate accounts protected as described in 4.2 and 4.3.</t>
+          <t>It applies to all employees and contractors, and to every system that stores or processes Quarterhour or customer data, including AWS, GitHub, Google Workspace, Stripe and the Quarterhour admin console.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>AC-006</t>
+          <t>AC-005</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>What password requirements apply to staff accounts?</t>
+          <t>Does the product support single sign-on (SAML or OIDC) for customer users?</t>
         </is>
       </c>
       <c r="C43" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -7727,7 +7739,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>4.3 Passwords</t>
+          <t>4.1 Single sign-on</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -7737,7 +7749,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>Passwords must be at least 14 characters long, unique to each system and stored in the company password manager. Passwords are never shared by email or chat.</t>
+          <t>Google Workspace is the company identity provider. Internal applications that support single sign-on must use it. A few tools that do not support single sign-on use separate accounts protected as described in 4.2 and 4.3.</t>
         </is>
       </c>
     </row>
@@ -7752,13 +7764,11 @@
           <t>What password requirements apply to staff accounts?</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+      <c r="C44" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -7767,7 +7777,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>5.3 Root and break-glass accounts</t>
+          <t>4.3 Passwords</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -7777,7 +7787,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t>The AWS root user is protected with a hardware security key, has no access keys and is used only for tasks that require it. A break-glass administrator account exists for emergencies. Its credentials are sealed in the password manager, and every use is logged and reviewed by the CTO.</t>
+          <t>Passwords must be at least 14 characters long, unique to each system and stored in the company password manager. Passwords are never shared by email or chat.</t>
         </is>
       </c>
     </row>
@@ -7792,51 +7802,51 @@
           <t>What password requirements apply to staff accounts?</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+      <c r="C45" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>1. Purpose</t>
+          <t>5.3 Root and break-glass accounts</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
+          <t>The AWS root user is protected with a hardware security key, has no access keys and is used only for tasks that require it. A break-glass administrator account exists for emergencies. Its credentials are sealed in the password manager, and every use is logged and reviewed by the CTO.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AC-007</t>
+          <t>AC-006</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>How often are user access rights reviewed?</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>1</v>
+          <t>What password requirements apply to staff accounts?</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>0.26</v>
+        <v>0.09</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -7845,7 +7855,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>7. Access reviews</t>
+          <t>2. Scope</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -7855,7 +7865,7 @@
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t>The CTO reviews user access to AWS, GitHub, Google Workspace and production database roles every quarter. The results and any changes are recorded in the access register.</t>
+          <t>It applies to all employees and contractors, and to every system that stores or processes Quarterhour or customer data, including AWS, GitHub, Google Workspace, Stripe and the Quarterhour admin console.</t>
         </is>
       </c>
     </row>
@@ -7870,13 +7880,11 @@
           <t>How often are user access rights reviewed?</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+      <c r="C47" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -7885,7 +7893,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>5.1 Production administrators</t>
+          <t>7. Access reviews</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -7895,7 +7903,7 @@
       </c>
       <c r="H47" s="3" t="inlineStr">
         <is>
-          <t>Administrator access to the production AWS account is limited to the CTO and two named senior engineers. The current list is kept in the access register.</t>
+          <t>The CTO reviews user access to AWS, GitHub, Google Workspace and production database roles every quarter. The results and any changes are recorded in the access register.</t>
         </is>
       </c>
     </row>
@@ -7912,11 +7920,11 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -7925,7 +7933,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>5.3 Root and break-glass accounts</t>
+          <t>5.1 Production administrators</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -7935,26 +7943,28 @@
       </c>
       <c r="H48" s="3" t="inlineStr">
         <is>
-          <t>The AWS root user is protected with a hardware security key, has no access keys and is used only for tasks that require it. A break-glass administrator account exists for emergencies. Its credentials are sealed in the password manager, and every use is logged and reviewed by the CTO.</t>
+          <t>Administrator access to the production AWS account is limited to the CTO and two named senior engineers. The current list is kept in the access register.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AC-008</t>
+          <t>AC-007</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>How is administrator access to production systems limited and controlled?</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>1</v>
+          <t>How often are user access rights reviewed?</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0.41</v>
+        <v>0.08</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -7963,7 +7973,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>5.1 Production administrators</t>
+          <t>5.3 Root and break-glass accounts</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -7973,7 +7983,7 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>Administrator access to the production AWS account is limited to the CTO and two named senior engineers. The current list is kept in the access register.</t>
+          <t>The AWS root user is protected with a hardware security key, has no access keys and is used only for tasks that require it. A break-glass administrator account exists for emergencies. Its credentials are sealed in the password manager, and every use is logged and reviewed by the CTO.</t>
         </is>
       </c>
     </row>
@@ -7989,10 +7999,10 @@
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>0.21</v>
+        <v>0.41</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -8001,7 +8011,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>5.2 Access to customer data</t>
+          <t>5.1 Production administrators</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -8011,7 +8021,7 @@
       </c>
       <c r="H50" s="3" t="inlineStr">
         <is>
-          <t>Support staff view customer accounts through the Quarterhour admin console, which limits what each role can see. Direct access to the production database is limited to on-call engineers, goes through AWS Systems Manager Session Manager, and is logged in AWS CloudTrail.</t>
+          <t>Administrator access to the production AWS account is limited to the CTO and two named senior engineers. The current list is kept in the access register.</t>
         </is>
       </c>
     </row>
@@ -8027,10 +8037,10 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -8039,7 +8049,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>5.3 Root and break-glass accounts</t>
+          <t>5.2 Access to customer data</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -8049,26 +8059,26 @@
       </c>
       <c r="H51" s="3" t="inlineStr">
         <is>
-          <t>The AWS root user is protected with a hardware security key, has no access keys and is used only for tasks that require it. A break-glass administrator account exists for emergencies. Its credentials are sealed in the password manager, and every use is logged and reviewed by the CTO.</t>
+          <t>Support staff view customer accounts through the Quarterhour admin console, which limits what each role can see. Direct access to the production database is limited to on-call engineers, goes through AWS Systems Manager Session Manager, and is logged in AWS CloudTrail.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>AC-009</t>
+          <t>AC-008</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Are shared or generic user accounts used?</t>
+          <t>How is administrator access to production systems limited and controlled?</t>
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>0.36</v>
+        <v>0.2</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -8077,7 +8087,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>3. Principles</t>
+          <t>5.3 Root and break-glass accounts</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -8087,7 +8097,7 @@
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>Every person has an individual, named account. Shared or generic accounts are not allowed, except the break-glass account described in section 5.3.</t>
+          <t>The AWS root user is protected with a hardware security key, has no access keys and is used only for tasks that require it. A break-glass administrator account exists for emergencies. Its credentials are sealed in the password manager, and every use is logged and reviewed by the CTO.</t>
         </is>
       </c>
     </row>
@@ -8103,10 +8113,10 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0.16</v>
+        <v>0.38</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -8115,7 +8125,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>5.3 Root and break-glass accounts</t>
+          <t>3. Principles</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -8125,7 +8135,7 @@
       </c>
       <c r="H53" s="3" t="inlineStr">
         <is>
-          <t>The AWS root user is protected with a hardware security key, has no access keys and is used only for tasks that require it. A break-glass administrator account exists for emergencies. Its credentials are sealed in the password manager, and every use is logged and reviewed by the CTO.</t>
+          <t>Every person has an individual, named account. Shared or generic accounts are not allowed, except the break-glass account described in section 5.3.</t>
         </is>
       </c>
     </row>
@@ -8140,70 +8150,70 @@
           <t>Are shared or generic user accounts used?</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+      <c r="C54" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2. Source code</t>
+          <t>5.3 Root and break-glass accounts</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
         <is>
-          <t>All code is stored in private GitHub repositories. Engineers use individual accounts with MFA. The main branch is protected, so nobody can push to it directly.</t>
+          <t>The AWS root user is protected with a hardware security key, has no access keys and is used only for tasks that require it. A break-glass administrator account exists for emergencies. Its credentials are sealed in the password manager, and every use is logged and reviewed by the CTO.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>AC-010</t>
+          <t>AC-009</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Who can access customer data in production, and is that access logged?</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>1</v>
+          <t>Are shared or generic user accounts used?</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0.36</v>
+        <v>0.08</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>5.2 Access to customer data</t>
+          <t>2. Source code</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>Support staff view customer accounts through the Quarterhour admin console, which limits what each role can see. Direct access to the production database is limited to on-call engineers, goes through AWS Systems Manager Session Manager, and is logged in AWS CloudTrail.</t>
+          <t>All code is stored in private GitHub repositories. Engineers use individual accounts with MFA. The main branch is protected, so nobody can push to it directly.</t>
         </is>
       </c>
     </row>
@@ -8218,13 +8228,11 @@
           <t>Who can access customer data in production, and is that access logged?</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+      <c r="C56" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0.11</v>
+        <v>0.38</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -8233,7 +8241,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2. Scope</t>
+          <t>5.2 Access to customer data</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -8243,7 +8251,7 @@
       </c>
       <c r="H56" s="3" t="inlineStr">
         <is>
-          <t>It applies to all employees and contractors, and to every system that stores or processes Quarterhour or customer data, including AWS, GitHub, Google Workspace, Stripe and the Quarterhour admin console.</t>
+          <t>Support staff view customer accounts through the Quarterhour admin console, which limits what each role can see. Direct access to the production database is limited to on-call engineers, goes through AWS Systems Manager Session Manager, and is logged in AWS CloudTrail.</t>
         </is>
       </c>
     </row>
@@ -8258,13 +8266,11 @@
           <t>Who can access customer data in production, and is that access logged?</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+      <c r="C57" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -8273,7 +8279,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>7. Access reviews</t>
+          <t>2. Scope</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -8283,45 +8289,47 @@
       </c>
       <c r="H57" s="3" t="inlineStr">
         <is>
-          <t>The CTO reviews user access to AWS, GitHub, Google Workspace and production database roles every quarter. The results and any changes are recorded in the access register.</t>
+          <t>It applies to all employees and contractors, and to every system that stores or processes Quarterhour or customer data, including AWS, GitHub, Google Workspace, Stripe and the Quarterhour admin console.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>CRY-001</t>
+          <t>AC-010</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Is customer data encrypted at rest?</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>1</v>
+          <t>Who can access customer data in production, and is that access logged?</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0.26</v>
+        <v>0.11</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2. Data at rest</t>
+          <t>5.1 Production administrators</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>Customer data stored in Amazon RDS, Amazon S3 and EBS volumes is encrypted at rest with AES-256 using AWS Key Management Service (KMS). Encryption is on by default for new storage, and a configuration check raises an alert if unencrypted storage is created.</t>
+          <t>Administrator access to the production AWS account is limited to the CTO and two named senior engineers. The current list is kept in the access register.</t>
         </is>
       </c>
     </row>
@@ -8337,10 +8345,10 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -8374,13 +8382,11 @@
           <t>Is customer data encrypted at rest?</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+      <c r="C60" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>0.09</v>
+        <v>0.24</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -8389,7 +8395,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>2. Data at rest</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -8399,26 +8405,28 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
+          <t>Customer data stored in Amazon RDS, Amazon S3 and EBS volumes is encrypted at rest with AES-256 using AWS Key Management Service (KMS). Encryption is on by default for new storage, and a configuration check raises an alert if unencrypted storage is created.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>CRY-002</t>
+          <t>CRY-001</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Is data encrypted in transit over public networks?</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>1</v>
+          <t>Is customer data encrypted at rest?</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>0.36</v>
+        <v>0.09</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -8427,7 +8435,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>3. Data in transit</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -8437,7 +8445,7 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>All public endpoints accept only HTTPS connections using TLS 1.2 or higher. HTTP requests are redirected to HTTPS and HSTS is enabled. Traffic between internal services and to the database also uses TLS.</t>
+          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
         </is>
       </c>
     </row>
@@ -8452,32 +8460,30 @@
           <t>Is data encrypted in transit over public networks?</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+      <c r="C62" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>0.09</v>
+        <v>0.35</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Encryption and Key Management Standard v1.1</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>8. Remote access</t>
+          <t>3. Data in transit</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>encryption-standard.docx</t>
         </is>
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>Quarterhour does not operate a corporate office network or VPN. Production servers are not reachable over SSH from the internet. Engineers connect through AWS Systems Manager Session Manager using their individual, MFA-protected identities.</t>
+          <t>All public endpoints accept only HTTPS connections using TLS 1.2 or higher. HTTP requests are redirected to HTTPS and HSTS is enabled. Traffic between internal services and to the database also uses TLS.</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8500,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
@@ -8524,38 +8530,40 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>CRY-003</t>
+          <t>CRY-002</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>How are encryption keys managed and protected?</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>1</v>
+          <t>Is data encrypted in transit over public networks?</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0.37</v>
+        <v>0.08</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>4. Key management</t>
+          <t>(start of document)</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
-          <t>Encryption keys are customer managed keys in AWS KMS. Automatic annual key rotation is enabled. IAM policies restrict the use of each key to the services and administrators that need it, and every use of a key is logged in AWS CloudTrail. Key material never leaves KMS.</t>
+          <t>FICTIONAL SAMPLE. Quarterhour, Inc. is a made-up company used to demonstrate this kit. • Document ID: QH-POL-11 • Version: 1.2 • Owner: Dana Whitfield, CTO • Approved by: Maya Okafor, CEO • Last reviewed: 8 August 2026 • Review cycle: at least annually</t>
         </is>
       </c>
     </row>
@@ -8571,10 +8579,10 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -8583,7 +8591,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>4. Key management</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -8593,7 +8601,7 @@
       </c>
       <c r="H65" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
+          <t>Encryption keys are customer managed keys in AWS KMS. Automatic annual key rotation is enabled. IAM policies restrict the use of each key to the services and administrators that need it, and every use of a key is logged in AWS CloudTrail. Key material never leaves KMS.</t>
         </is>
       </c>
     </row>
@@ -8609,67 +8617,67 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Encryption and Key Management Standard v1.1</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>6. Encryption</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>encryption-standard.docx</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>All backups and snapshots are encrypted with AES-256 using AWS Key Management Service (KMS) keys.</t>
+          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>CRY-004</t>
+          <t>CRY-003</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Are encryption keys rotated on a schedule?</t>
+          <t>How are encryption keys managed and protected?</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>4. Key management</t>
+          <t>6. Encryption</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>Encryption keys are customer managed keys in AWS KMS. Automatic annual key rotation is enabled. IAM policies restrict the use of each key to the services and administrators that need it, and every use of a key is logged in AWS CloudTrail. Key material never leaves KMS.</t>
+          <t>All backups and snapshots are encrypted with AES-256 using AWS Key Management Service (KMS) keys.</t>
         </is>
       </c>
     </row>
@@ -8685,10 +8693,10 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -8697,7 +8705,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>4. Key management</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -8707,7 +8715,7 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
+          <t>Encryption keys are customer managed keys in AWS KMS. Automatic annual key rotation is enabled. IAM policies restrict the use of each key to the services and administrators that need it, and every use of a key is logged in AWS CloudTrail. Key material never leaves KMS.</t>
         </is>
       </c>
     </row>
@@ -8722,70 +8730,70 @@
           <t>Are encryption keys rotated on a schedule?</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+      <c r="C69" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Encryption and Key Management Standard v1.1</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>6. Encryption</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>encryption-standard.docx</t>
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>All backups and snapshots are encrypted with AES-256 using AWS Key Management Service (KMS) keys.</t>
+          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>CRY-005</t>
+          <t>CRY-004</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>How are application secrets such as API keys and passwords stored?</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="n">
-        <v>1</v>
+          <t>Are encryption keys rotated on a schedule?</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0.53</v>
+        <v>0.11</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>5. Application secrets</t>
+          <t>6. Encryption</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H70" s="3" t="inlineStr">
         <is>
-          <t>API keys, database passwords and other secrets are stored in AWS Secrets Manager. Secrets must never be committed to source code. Secret scanning is turned on for all code repositories.</t>
+          <t>All backups and snapshots are encrypted with AES-256 using AWS Key Management Service (KMS) keys.</t>
         </is>
       </c>
     </row>
@@ -8801,29 +8809,29 @@
         </is>
       </c>
       <c r="C71" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0.18</v>
+        <v>0.53</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Encryption and Key Management Standard v1.1</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>7. Key vendors</t>
+          <t>5. Application secrets</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>encryption-standard.docx</t>
         </is>
       </c>
       <c r="H71" s="3" t="inlineStr">
         <is>
-          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
+          <t>API keys, database passwords and other secrets are stored in AWS Secrets Manager. Secrets must never be committed to source code. Secret scanning is turned on for all code repositories.</t>
         </is>
       </c>
     </row>
@@ -8838,70 +8846,70 @@
           <t>How are application secrets such as API keys and passwords stored?</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+      <c r="C72" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2. Source code</t>
+          <t>7. Key vendors</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
         <is>
-          <t>All code is stored in private GitHub repositories. Engineers use individual accounts with MFA. The main branch is protected, so nobody can push to it directly.</t>
+          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>CRY-006</t>
+          <t>CRY-005</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Can customers manage their own encryption keys?</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>1</v>
+          <t>How are application secrets such as API keys and passwords stored?</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.27</v>
+        <v>0.12</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>4. Key management</t>
+          <t>2. Source code</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H73" s="3" t="inlineStr">
         <is>
-          <t>Encryption keys are customer managed keys in AWS KMS. Automatic annual key rotation is enabled. IAM policies restrict the use of each key to the services and administrators that need it, and every use of a key is logged in AWS CloudTrail. Key material never leaves KMS.</t>
+          <t>All code is stored in private GitHub repositories. Engineers use individual accounts with MFA. The main branch is protected, so nobody can push to it directly.</t>
         </is>
       </c>
     </row>
@@ -8917,10 +8925,10 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -8929,7 +8937,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>4. Key management</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -8939,7 +8947,7 @@
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
+          <t>Encryption keys are customer managed keys in AWS KMS. Automatic annual key rotation is enabled. IAM policies restrict the use of each key to the services and administrators that need it, and every use of a key is logged in AWS CloudTrail. Key material never leaves KMS.</t>
         </is>
       </c>
     </row>
@@ -8954,72 +8962,70 @@
           <t>Can customers manage their own encryption keys?</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+      <c r="C75" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Encryption and Key Management Standard v1.1</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>6. Encryption</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>encryption-standard.docx</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>All backups and snapshots are encrypted with AES-256 using AWS Key Management Service (KMS) keys.</t>
+          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>DAT-001</t>
+          <t>CRY-006</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>What types of customer data does the service store?</t>
+          <t>Can customers manage their own encryption keys?</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>1 (weak)</t>
+          <t>3 (weak)</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>2. Vendor register</t>
+          <t>6. Encryption</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>Quarterhour keeps a register of vendors that store or process company or customer data. For each vendor it records the data involved, the risk level and the contract owner. Vendors that process customer personal data are also listed as subprocessors on the public subprocessor list.</t>
+          <t>All backups and snapshots are encrypted with AES-256 using AWS Key Management Service (KMS) keys.</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9042,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>2 (weak)</t>
+          <t>1 (weak)</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
@@ -9076,68 +9082,70 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>3. Severity levels</t>
+          <t>2. Vendor register</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>SEV1: confirmed or likely exposure of customer data, or the service is down for all customers.</t>
+          <t>Quarterhour keeps a register of vendors that store or process company or customer data. For each vendor it records the data involved, the risk level and the contract owner. Vendors that process customer personal data are also listed as subprocessors on the public subprocessor list.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>DAT-002</t>
+          <t>DAT-001</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>In which countries or cloud regions is customer data stored and processed?</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>1</v>
+          <t>What types of customer data does the service store?</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>5. Backup location</t>
+          <t>3. Severity levels</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>Backups are copied to the AWS us-west-2 region (United States), into a separate AWS account that is used only for backups.</t>
+          <t>SEV1: confirmed or likely exposure of customer data, or the service is down for all customers.</t>
         </is>
       </c>
     </row>
@@ -9153,10 +9161,10 @@
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
@@ -9165,7 +9173,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>1. Purpose</t>
+          <t>5. Backup location</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -9175,7 +9183,7 @@
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>To make sure customer data can be restored after accidental deletion, corruption, or the loss of a hosting region.</t>
+          <t>Backups are copied to the AWS us-west-2 region (United States), into a separate AWS account that is used only for backups.</t>
         </is>
       </c>
     </row>
@@ -9191,10 +9199,10 @@
         </is>
       </c>
       <c r="C81" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -9203,7 +9211,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>2. Scope</t>
+          <t>1. Purpose</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -9213,135 +9221,137 @@
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>This policy covers the production PostgreSQL database (Amazon RDS) and customer file uploads stored in Amazon S3. Production runs in the AWS us-east-1 region (United States).</t>
+          <t>To make sure customer data can be restored after accidental deletion, corruption, or the loss of a hosting region.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>DAT-003</t>
+          <t>DAT-002</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>How is each customer's data kept separate from other customers' data?</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>1 (weak)</t>
-        </is>
+          <t>In which countries or cloud regions is customer data stored and processed?</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>5. Environments</t>
+          <t>2. Scope</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>Development, staging and production are separate. Staging and production run in separate AWS accounts. Production customer data is never copied to development or staging; those environments use synthetic test data.</t>
+          <t>This policy covers the production PostgreSQL database (Amazon RDS) and customer file uploads stored in Amazon S3. Production runs in the AWS us-east-1 region (United States).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>DAT-004</t>
+          <t>DAT-003</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>How long is customer data kept, and how is it deleted when the contract ends?</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>1</v>
+          <t>How is each customer's data kept separate from other customers' data?</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>1 (weak)</t>
+        </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>7. Access to backups</t>
+          <t>5. Environments</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>Only the CTO and one named senior engineer can restore or delete backups. The backup account blocks deletion of snapshots before the end of their retention period.</t>
+          <t>Development, staging and production are separate. Staging and production run in separate AWS accounts. Production customer data is never copied to development or staging; those environments use synthetic test data.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>DAT-004</t>
+          <t>DAT-003</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>How long is customer data kept, and how is it deleted when the contract ends?</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>2</v>
+          <t>How is each customer's data kept separate from other customers' data?</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>2 (weak)</t>
+        </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>8. Ending a vendor relationship</t>
+          <t>4.1 Single sign-on</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>When a vendor is no longer used, its access is removed and it is asked to confirm deletion or return of our data.</t>
+          <t>Google Workspace is the company identity provider. Internal applications that support single sign-on must use it. A few tools that do not support single sign-on use separate accounts protected as described in 4.2 and 4.3.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>DAT-004</t>
+          <t>DAT-003</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>How long is customer data kept, and how is it deleted when the contract ends?</t>
+          <t>How is each customer's data kept separate from other customers' data?</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -9350,7 +9360,7 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
@@ -9359,7 +9369,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>5. Backup location</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -9369,57 +9379,57 @@
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2. To make sure customer data can be restored after accidental deletion, corruption, or the loss of a hosting region.</t>
+          <t>Backups are copied to the AWS us-west-2 region (United States), into a separate AWS account that is used only for backups.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>DAT-005</t>
+          <t>DAT-004</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Does the company offer a data processing agreement (DPA) to customers?</t>
+          <t>How long is customer data kept, and how is it deleted when the contract ends?</t>
         </is>
       </c>
       <c r="C86" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>3. Assessment before use</t>
+          <t>7. Access to backups</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Before a new vendor receives customer data: • the contract owner completes a vendor risk review; • for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire; • a data processing agreement is signed if the vendor will process personal data. • The CTO approves every high-risk vendor.</t>
+          <t>Only the CTO and one named senior engineer can restore or delete backups. The backup account blocks deletion of snapshots before the end of their retention period.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>DAT-005</t>
+          <t>DAT-004</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Does the company offer a data processing agreement (DPA) to customers?</t>
+          <t>How long is customer data kept, and how is it deleted when the contract ends?</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -9428,43 +9438,43 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>4. Retention</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
+          <t>Automated database backups are kept for 35 days. • One snapshot a month is kept for 12 months. • Previous versions of S3 objects are kept for 35 days.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>DAT-006</t>
+          <t>DAT-004</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Is customer data used to train artificial intelligence or machine learning models?</t>
+          <t>How long is customer data kept, and how is it deleted when the contract ends?</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>1 (weak)</t>
+          <t>3 (weak)</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
@@ -9472,119 +9482,121 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>9. Training</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>Engineers complete secure coding training based on the OWASP Top 10 when they join and every year after that.</t>
+          <t>Backup and Recovery Policy v1.2. To make sure customer data can be restored after accidental deletion, corruption, or the loss of a hosting region.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>DAT-007</t>
+          <t>DAT-005</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Is production customer data used in development or test environments?</t>
+          <t>Does the company offer a data processing agreement (DPA) to customers?</t>
         </is>
       </c>
       <c r="C89" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.4</v>
+        <v>0.21</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>5. Environments</t>
+          <t>3. Assessment before use</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>Development, staging and production are separate. Staging and production run in separate AWS accounts. Production customer data is never copied to development or staging; those environments use synthetic test data.</t>
+          <t>Before a new vendor receives customer data: • the contract owner completes a vendor risk review; • for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire; • a data processing agreement is signed if the vendor will process personal data. • The CTO approves every high-risk vendor.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>DAT-007</t>
+          <t>DAT-005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Is production customer data used in development or test environments?</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>2</v>
+          <t>Does the company offer a data processing agreement (DPA) to customers?</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>2 (weak)</t>
+        </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Encryption and Key Management Standard v1.1</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>8. Restore testing</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>encryption-standard.docx</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>Every quarter, engineering restores the production database from backup into an isolated test environment, checks that the data is complete, and records the result and the time taken. The restored copy is deleted after the test.</t>
+          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>DAT-007</t>
+          <t>DAT-006</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Is production customer data used in development or test environments?</t>
+          <t>Is customer data used to train artificial intelligence or machine learning models?</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>1 (weak)</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -9593,7 +9605,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>9. Training</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -9603,177 +9615,175 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2. To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
+          <t>Engineers complete secure coding training based on the OWASP Top 10 when they join and every year after that.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>DAT-008</t>
+          <t>DAT-007</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>How does the company handle requests from individuals to access or delete their personal data?</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>1 (weak)</t>
-        </is>
+          <t>Is production customer data used in development or test environments?</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.12</v>
+        <v>0.39</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>6. Joiners, movers and leavers</t>
+          <t>5. Environments</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>New access is requested through a ticket and approved by the person's manager before it is granted.</t>
+          <t>Development, staging and production are separate. Staging and production run in separate AWS accounts. Production customer data is never copied to development or staging; those environments use synthetic test data.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>DAT-009</t>
+          <t>DAT-007</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Does the company classify data by sensitivity?</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>1 (weak)</t>
-        </is>
+          <t>Is production customer data used in development or test environments?</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.08</v>
+        <v>0.19</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>4. Contracts</t>
+          <t>8. Restore testing</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>Vendor contracts must include confidentiality obligations and security requirements, plus data protection terms where personal data is involved.</t>
+          <t>Every quarter, engineering restores the production database from backup into an isolated test environment, checks that the data is complete, and records the result and the time taken. The restored copy is deleted after the test.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>DAT-010</t>
+          <t>DAT-007</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Does the company publish a privacy policy that covers the service?</t>
+          <t>Is production customer data used in development or test environments?</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>1 (weak)</t>
+          <t>3 (weak)</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>2. Scope</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>This policy covers the production PostgreSQL database (Amazon RDS) and customer file uploads stored in Amazon S3. Production runs in the AWS us-east-1 region (United States).</t>
+          <t>Secure Development Policy v1.2. To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>BCK-001</t>
+          <t>DAT-008</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>How often is customer data backed up?</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="n">
-        <v>1</v>
+          <t>How does the company handle requests from individuals to access or delete their personal data?</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>1 (weak)</t>
+        </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.21</v>
+        <v>0.12</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>3. Backup frequency</t>
+          <t>6. Joiners, movers and leavers</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>Amazon RDS takes an automated snapshot of the production database every day and keeps transaction logs for point-in-time recovery. The database can be restored to any point within the retention period, normally to within 5 minutes.</t>
+          <t>New access is requested through a ticket and approved by the person's manager before it is granted.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>BCK-001</t>
+          <t>DAT-008</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>How often is customer data backed up?</t>
+          <t>How does the company handle requests from individuals to access or delete their personal data?</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -9782,7 +9792,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
@@ -9791,7 +9801,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>4. Retention</t>
+          <t>7. Access to backups</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -9801,142 +9811,146 @@
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>Automated database backups are kept for 35 days. • One snapshot a month is kept for 12 months. • Previous versions of S3 objects are kept for 35 days.</t>
+          <t>Only the CTO and one named senior engineer can restore or delete backups. The backup account blocks deletion of snapshots before the end of their retention period.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>BCK-002</t>
+          <t>DAT-008</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Are backups encrypted?</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="n">
-        <v>1</v>
+          <t>How does the company handle requests from individuals to access or delete their personal data?</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>0.52</v>
+        <v>0.08</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>6. Encryption</t>
+          <t>8. Ending a vendor relationship</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>All backups and snapshots are encrypted with AES-256 using AWS Key Management Service (KMS) keys.</t>
+          <t>When a vendor is no longer used, its access is removed and it is asked to confirm deletion or return of our data.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>BCK-002</t>
+          <t>DAT-009</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Are backups encrypted?</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="n">
-        <v>2</v>
+          <t>Does the company classify data by sensitivity?</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>1 (weak)</t>
+        </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>0.19</v>
+        <v>0.08</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>2. Data at rest</t>
+          <t>4. Contracts</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>Customer data stored in Amazon RDS, Amazon S3 and EBS volumes is encrypted at rest with AES-256 using AWS Key Management Service (KMS). Encryption is on by default for new storage, and a configuration check raises an alert if unencrypted storage is created.</t>
+          <t>Vendor contracts must include confidentiality obligations and security requirements, plus data protection terms where personal data is involved.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>BCK-002</t>
+          <t>DAT-010</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Are backups encrypted?</t>
+          <t>Does the company publish a privacy policy that covers the service?</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>1 (weak)</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>2. Scope</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
+          <t>This policy covers the production PostgreSQL database (Amazon RDS) and customer file uploads stored in Amazon S3. Production runs in the AWS us-east-1 region (United States).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>BCK-003</t>
+          <t>BCK-001</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Are backups stored in a separate location from the production systems?</t>
+          <t>How often is customer data backed up?</t>
         </is>
       </c>
       <c r="C100" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -9945,7 +9959,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>5. Backup location</t>
+          <t>3. Backup frequency</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -9955,57 +9969,57 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>Backups are copied to the AWS us-west-2 region (United States), into a separate AWS account that is used only for backups.</t>
+          <t>Amazon RDS takes an automated snapshot of the production database every day and keeps transaction logs for point-in-time recovery. The database can be restored to any point within the retention period, normally to within 5 minutes.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>BCK-003</t>
+          <t>BCK-001</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Are backups stored in a separate location from the production systems?</t>
+          <t>How often is customer data backed up?</t>
         </is>
       </c>
       <c r="C101" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.19</v>
+        <v>0.14</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>5. Disaster recovery (page 1)</t>
+          <t>4. Retention</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>business-continuity-plan.pdf</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>If the us-east-1 region becomes unavailable, the team rebuilds the service in the us-west-2 region from the cross-region backups described in the Backup and Recovery Policy, using infrastructure-as-code templates. The CTO decides when to start regional recovery.</t>
+          <t>Automated database backups are kept for 35 days. • One snapshot a month is kept for 12 months. • Previous versions of S3 objects are kept for 35 days.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>BCK-003</t>
+          <t>BCK-001</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Are backups stored in a separate location from the production systems?</t>
+          <t>How often is customer data backed up?</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -10014,45 +10028,45 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>4. Retention</t>
+          <t>7. Key vendors</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>Automated database backups are kept for 35 days. • One snapshot a month is kept for 12 months. • Previous versions of S3 objects are kept for 35 days.</t>
+          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>BCK-004</t>
+          <t>BCK-002</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>How long are backups kept?</t>
+          <t>Are backups encrypted?</t>
         </is>
       </c>
       <c r="C103" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0.31</v>
+        <v>0.64</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
@@ -10061,7 +10075,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>4. Retention</t>
+          <t>6. Encryption</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -10071,102 +10085,104 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>Automated database backups are kept for 35 days. • One snapshot a month is kept for 12 months. • Previous versions of S3 objects are kept for 35 days.</t>
+          <t>All backups and snapshots are encrypted with AES-256 using AWS Key Management Service (KMS) keys.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>BCK-004</t>
+          <t>BCK-002</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>How long are backups kept?</t>
+          <t>Are backups encrypted?</t>
         </is>
       </c>
       <c r="C104" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Encryption and Key Management Standard v1.1</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>7. Access to backups</t>
+          <t>2. Data at rest</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>encryption-standard.docx</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>Only the CTO and one named senior engineer can restore or delete backups. The backup account blocks deletion of snapshots before the end of their retention period.</t>
+          <t>Customer data stored in Amazon RDS, Amazon S3 and EBS volumes is encrypted at rest with AES-256 using AWS Key Management Service (KMS). Encryption is on by default for new storage, and a configuration check raises an alert if unencrypted storage is created.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>BCK-004</t>
+          <t>BCK-002</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>How long are backups kept?</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="n">
-        <v>3</v>
+          <t>Are backups encrypted?</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Encryption and Key Management Standard v1.1</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>3. Backup frequency</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>encryption-standard.docx</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>Amazon RDS takes an automated snapshot of the production database every day and keeps transaction logs for point-in-time recovery. The database can be restored to any point within the retention period, normally to within 5 minutes.</t>
+          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>BCK-005</t>
+          <t>BCK-003</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Are restores from backup tested, and how often?</t>
+          <t>Are backups stored in a separate location from the production systems?</t>
         </is>
       </c>
       <c r="C106" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -10175,7 +10191,7 @@
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>8. Restore testing</t>
+          <t>5. Backup location</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -10185,28 +10201,26 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>Every quarter, engineering restores the production database from backup into an isolated test environment, checks that the data is complete, and records the result and the time taken. The restored copy is deleted after the test.</t>
+          <t>Backups are copied to the AWS us-west-2 region (United States), into a separate AWS account that is used only for backups.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>BCK-005</t>
+          <t>BCK-003</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Are restores from backup tested, and how often?</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+          <t>Are backups stored in a separate location from the production systems?</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
@@ -10215,7 +10229,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>8. Testing (page 2)</t>
+          <t>5. Disaster recovery (page 1)</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -10225,28 +10239,26 @@
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>The disaster recovery procedure is tested at least once a year by restoring the service in us-west-2. This plan is reviewed every year and after each major incident.</t>
+          <t>If the us-east-1 region becomes unavailable, the team rebuilds the service in the us-west-2 region from the cross-region backups described in the Backup and Recovery Policy, using infrastructure-as-code templates. The CTO decides when to start regional recovery.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>BCK-005</t>
+          <t>BCK-003</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Are restores from backup tested, and how often?</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+          <t>Are backups stored in a separate location from the production systems?</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -10255,7 +10267,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>4. Retention</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -10265,26 +10277,26 @@
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2. To make sure customer data can be restored after accidental deletion, corruption, or the loss of a hosting region.</t>
+          <t>Automated database backups are kept for 35 days. • One snapshot a month is kept for 12 months. • Previous versions of S3 objects are kept for 35 days.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>BCK-006</t>
+          <t>BCK-004</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Who can access or delete backups?</t>
+          <t>How long are backups kept?</t>
         </is>
       </c>
       <c r="C109" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -10293,7 +10305,7 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>7. Access to backups</t>
+          <t>4. Retention</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -10303,28 +10315,26 @@
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>Only the CTO and one named senior engineer can restore or delete backups. The backup account blocks deletion of snapshots before the end of their retention period.</t>
+          <t>Automated database backups are kept for 35 days. • One snapshot a month is kept for 12 months. • Previous versions of S3 objects are kept for 35 days.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>BCK-006</t>
+          <t>BCK-004</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Who can access or delete backups?</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+          <t>How long are backups kept?</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -10333,7 +10343,7 @@
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>7. Access to backups</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -10343,19 +10353,19 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2. To make sure customer data can be restored after accidental deletion, corruption, or the loss of a hosting region.</t>
+          <t>Only the CTO and one named senior engineer can restore or delete backups. The backup account blocks deletion of snapshots before the end of their retention period.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>BCK-006</t>
+          <t>BCK-004</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Who can access or delete backups?</t>
+          <t>How long are backups kept?</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -10364,83 +10374,85 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>8. Ending a vendor relationship</t>
+          <t>3. Backup frequency</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>When a vendor is no longer used, its access is removed and it is asked to confirm deletion or return of our data.</t>
+          <t>Amazon RDS takes an automated snapshot of the production database every day and keeps transaction logs for point-in-time recovery. The database can be restored to any point within the retention period, normally to within 5 minutes.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>BCP-001</t>
+          <t>BCK-005</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Does the company have a business continuity plan?</t>
+          <t>Are restores from backup tested, and how often?</t>
         </is>
       </c>
       <c r="C112" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>8. Restore testing</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>business-continuity-plan.pdf</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0. This plan explains how Quarterhour keeps its service running, or restores it quickly, after a serious disruption.</t>
+          <t>Every quarter, engineering restores the production database from backup into an isolated test environment, checks that the data is complete, and records the result and the time taken. The restored copy is deleted after the test.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>BCP-001</t>
+          <t>BCK-005</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Does the company have a business continuity plan?</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="n">
-        <v>2</v>
+          <t>Are restores from backup tested, and how often?</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>2 (weak)</t>
+        </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -10449,7 +10461,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>1. Purpose (page 1)</t>
+          <t>8. Testing (page 2)</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -10459,178 +10471,184 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>This plan explains how Quarterhour keeps its service running, or restores it quickly, after a serious disruption.</t>
+          <t>The disaster recovery procedure is tested at least once a year by restoring the service in us-west-2. This plan is reviewed every year and after each major incident.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>BCP-001</t>
+          <t>BCK-005</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Does the company have a business continuity plan?</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="n">
-        <v>3</v>
+          <t>Are restores from backup tested, and how often?</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>(start of document)</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>business-continuity-plan.pdf</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan FICTIONAL SAMPLE. Quarterhour, Inc. is a made-up company used to demonstrate this kit. Any resemblance to a real company is coincidental. Document ID QH-POL-08 Version 1.0 Owner Dana Whitfield, CTO Approved by Maya Okafor, CEO Last reviewed 25 June 2026 Review cycle At least annually</t>
+          <t>Backup and Recovery Policy v1.2. To make sure customer data can be restored after accidental deletion, corruption, or the loss of a hosting region.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>BCP-002</t>
+          <t>BCK-006</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Does the company have a disaster recovery plan for the production service?</t>
+          <t>Who can access or delete backups?</t>
         </is>
       </c>
       <c r="C115" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>7. Access to backups</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>business-continuity-plan.pdf</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0. This plan explains how Quarterhour keeps its service running, or restores it quickly, after a serious disruption.</t>
+          <t>Only the CTO and one named senior engineer can restore or delete backups. The backup account blocks deletion of snapshots before the end of their retention period.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>BCP-002</t>
+          <t>BCK-006</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Does the company have a disaster recovery plan for the production service?</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v>2</v>
+          <t>Who can access or delete backups?</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>2 (weak)</t>
+        </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>8. Testing (page 2)</t>
+          <t>6. Encryption</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>business-continuity-plan.pdf</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>The disaster recovery procedure is tested at least once a year by restoring the service in us-west-2. This plan is reviewed every year and after each major incident.</t>
+          <t>All backups and snapshots are encrypted with AES-256 using AWS Key Management Service (KMS) keys.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>BCP-002</t>
+          <t>BCK-006</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Does the company have a disaster recovery plan for the production service?</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="n">
-        <v>3</v>
+          <t>Who can access or delete backups?</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>5. Disaster recovery (page 1)</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>business-continuity-plan.pdf</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>If the us-east-1 region becomes unavailable, the team rebuilds the service in the us-west-2 region from the cross-region backups described in the Backup and Recovery Policy, using infrastructure-as-code templates. The CTO decides when to start regional recovery.</t>
+          <t>Backup and Recovery Policy v1.2. To make sure customer data can be restored after accidental deletion, corruption, or the loss of a hosting region.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>BCP-003</t>
+          <t>BCP-001</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>What are the recovery time objective (RTO) and recovery point objective (RPO) for the service?</t>
+          <t>Does the company have a business continuity plan?</t>
         </is>
       </c>
       <c r="C118" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.46</v>
+        <v>0.24</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
@@ -10639,7 +10657,7 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>3. Recovery objectives (page 1)</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
@@ -10649,64 +10667,64 @@
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>Recovery time objective (RTO): 8 hours. • Recovery point objective (RPO): 1 hour.</t>
+          <t>Business Continuity and Disaster Recovery Plan v1.0. This plan explains how Quarterhour keeps its service running, or restores it quickly, after a serious disruption.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>BCP-004</t>
+          <t>BCP-001</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>How often are the business continuity and disaster recovery plans tested?</t>
+          <t>Does the company have a business continuity plan?</t>
         </is>
       </c>
       <c r="C119" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>9. Testing</t>
+          <t>1. Purpose (page 1)</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>business-continuity-plan.pdf</t>
         </is>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>This plan is tested with a tabletop exercise at least once a year. The results and any improvements are recorded.</t>
+          <t>This plan explains how Quarterhour keeps its service running, or restores it quickly, after a serious disruption.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>BCP-004</t>
+          <t>BCP-001</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>How often are the business continuity and disaster recovery plans tested?</t>
+          <t>Does the company have a business continuity plan?</t>
         </is>
       </c>
       <c r="C120" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
@@ -10715,7 +10733,7 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>8. Testing (page 2)</t>
+          <t>(start of document)</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -10725,26 +10743,26 @@
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>The disaster recovery procedure is tested at least once a year by restoring the service in us-west-2. This plan is reviewed every year and after each major incident.</t>
+          <t>Business Continuity and Disaster Recovery Plan FICTIONAL SAMPLE. Quarterhour, Inc. is a made-up company used to demonstrate this kit. Any resemblance to a real company is coincidental. Document ID QH-POL-08 Version 1.0 Owner Dana Whitfield, CTO Approved by Maya Okafor, CEO Last reviewed 25 June 2026 Review cycle At least annually</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>BCP-004</t>
+          <t>BCP-002</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>How often are the business continuity and disaster recovery plans tested?</t>
+          <t>Does the company have a disaster recovery plan for the production service?</t>
         </is>
       </c>
       <c r="C121" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
@@ -10770,19 +10788,19 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>BCP-005</t>
+          <t>BCP-002</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Is the production environment built for high availability?</t>
+          <t>Does the company have a disaster recovery plan for the production service?</t>
         </is>
       </c>
       <c r="C122" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
@@ -10791,7 +10809,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>4. Resilience (page 1)</t>
+          <t>5. Disaster recovery (page 1)</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -10801,26 +10819,26 @@
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>The application runs on AWS across two availability zones in the us-east-1 region. The database uses Amazon RDS Multi-AZ with automatic failover.</t>
+          <t>If the us-east-1 region becomes unavailable, the team rebuilds the service in the us-west-2 region from the cross-region backups described in the Backup and Recovery Policy, using infrastructure-as-code templates. The CTO decides when to start regional recovery.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>BCP-007</t>
+          <t>BCP-002</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>How are customers told about outages and service problems?</t>
+          <t>Does the company have a disaster recovery plan for the production service?</t>
         </is>
       </c>
       <c r="C123" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
@@ -10829,7 +10847,7 @@
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>7. Communication (page 2)</t>
+          <t>8. Testing (page 2)</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -10839,64 +10857,64 @@
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>During an outage, updates are posted on the public status page and emailed to customer account administrators.</t>
+          <t>The disaster recovery procedure is tested at least once a year by restoring the service in us-west-2. This plan is reviewed every year and after each major incident.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>BCP-007</t>
+          <t>BCP-003</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>How are customers told about outages and service problems?</t>
+          <t>What are the recovery time objective (RTO) and recovery point objective (RPO) for the service?</t>
         </is>
       </c>
       <c r="C124" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0.15</v>
+        <v>0.49</v>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>6. Subprocessor changes</t>
+          <t>3. Recovery objectives (page 1)</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>business-continuity-plan.pdf</t>
         </is>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>Customers are told at least 30 days before a new subprocessor starts processing their personal data. Notice is sent by email to customer account administrators and the public subprocessor list is updated.</t>
+          <t>Recovery time objective (RTO): 8 hours. • Recovery point objective (RPO): 1 hour.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>IR-001</t>
+          <t>BCP-004</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Does the company have a documented incident response plan?</t>
+          <t>How often are the business continuity and disaster recovery plans tested?</t>
         </is>
       </c>
       <c r="C125" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
@@ -10905,7 +10923,7 @@
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>9. Testing</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -10915,218 +10933,218 @@
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1. This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
+          <t>This plan is tested with a tabletop exercise at least once a year. The results and any improvements are recorded.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>IR-001</t>
+          <t>BCP-004</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Does the company have a documented incident response plan?</t>
+          <t>How often are the business continuity and disaster recovery plans tested?</t>
         </is>
       </c>
       <c r="C126" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>1. Purpose</t>
+          <t>8. Testing (page 2)</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>business-continuity-plan.pdf</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
+          <t>The disaster recovery procedure is tested at least once a year by restoring the service in us-west-2. This plan is reviewed every year and after each major incident.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>IR-001</t>
+          <t>BCP-004</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Does the company have a documented incident response plan?</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+          <t>How often are the business continuity and disaster recovery plans tested?</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>6. Response steps</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>business-continuity-plan.pdf</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>Triage: confirm the incident and set its severity. • Contain: limit the damage, for example by revoking credentials or isolating a resource. • Eradicate and recover: remove the cause and restore normal service from known-good sources. • Preserve evidence: keep relevant logs and snapshots until the post-incident review is complete. • Close: confirm the issue is resolved and record the timeline.</t>
+          <t>Business Continuity and Disaster Recovery Plan v1.0. This plan explains how Quarterhour keeps its service running, or restores it quickly, after a serious disruption.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>IR-002</t>
+          <t>BCP-005</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>How quickly will customers be notified of a security incident that affects their data?</t>
+          <t>Is the production environment built for high availability?</t>
         </is>
       </c>
       <c r="C128" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0.36</v>
+        <v>0.16</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>7. Customer notification</t>
+          <t>4. Resilience (page 1)</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>business-continuity-plan.pdf</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>If a security incident affects customer data, Quarterhour notifies the affected customers without undue delay and no later than 72 hours after confirming the incident. The notice explains what happened, which data was involved, what we are doing about it and who to contact.</t>
+          <t>The application runs on AWS across two availability zones in the us-east-1 region. The database uses Amazon RDS Multi-AZ with automatic failover.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>IR-003</t>
+          <t>BCP-007</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Who leads incident response, and are roles defined?</t>
+          <t>How are customers told about outages and service problems?</t>
         </is>
       </c>
       <c r="C129" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>4. Roles</t>
+          <t>7. Communication (page 2)</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>business-continuity-plan.pdf</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>Incident Lead: the CTO (backup: the on-call senior engineer). Runs the response and makes technical decisions. • Communications Lead: the CEO. Approves all messages to customers, regulators and partners. • Responders: engineers assigned by the Incident Lead.</t>
+          <t>During an outage, updates are posted on the public status page and emailed to customer account administrators.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>IR-003</t>
+          <t>BCP-007</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Who leads incident response, and are roles defined?</t>
+          <t>How are customers told about outages and service problems?</t>
         </is>
       </c>
       <c r="C130" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>0.21</v>
+        <v>0.14</v>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>9. Roles (page 2)</t>
+          <t>6. Subprocessor changes</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>business-continuity-plan.pdf</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>The CTO leads recovery. The CEO leads communication with customers.</t>
+          <t>Customers are told at least 30 days before a new subprocessor starts processing their personal data. Notice is sent by email to customer account administrators and the public subprocessor list is updated.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>IR-003</t>
+          <t>BCP-007</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Who leads incident response, and are roles defined?</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="n">
-        <v>3</v>
+          <t>How are customers told about outages and service problems?</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
@@ -11135,7 +11153,7 @@
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>3. Severity levels</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -11145,26 +11163,26 @@
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1. This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
+          <t>SEV1: confirmed or likely exposure of customer data, or the service is down for all customers. • SEV2: a limited security issue or a partial outage. • SEV3: a suspicious event with no confirmed impact.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>IR-004</t>
+          <t>IR-001</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Is the incident response plan tested at least once a year?</t>
+          <t>Does the company have a documented incident response plan?</t>
         </is>
       </c>
       <c r="C132" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -11173,7 +11191,7 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>9. Testing</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -11183,26 +11201,26 @@
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>This plan is tested with a tabletop exercise at least once a year. The results and any improvements are recorded.</t>
+          <t>Incident Response Plan v1.1. This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>IR-004</t>
+          <t>IR-001</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Is the incident response plan tested at least once a year?</t>
+          <t>Does the company have a documented incident response plan?</t>
         </is>
       </c>
       <c r="C133" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
@@ -11211,7 +11229,7 @@
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>1. Purpose</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
@@ -11221,64 +11239,66 @@
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1. This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
+          <t>This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>IR-004</t>
+          <t>IR-001</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Is the incident response plan tested at least once a year?</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="n">
-        <v>3</v>
+          <t>Does the company have a documented incident response plan?</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>8. Testing (page 2)</t>
+          <t>6. Response steps</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>business-continuity-plan.pdf</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>The disaster recovery procedure is tested at least once a year by restoring the service in us-west-2. This plan is reviewed every year and after each major incident.</t>
+          <t>Triage: confirm the incident and set its severity. • Contain: limit the damage, for example by revoking credentials or isolating a resource. • Eradicate and recover: remove the cause and restore normal service from known-good sources. • Preserve evidence: keep relevant logs and snapshots until the post-incident review is complete. • Close: confirm the issue is resolved and record the timeline.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>IR-005</t>
+          <t>IR-002</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Are security incidents recorded and reviewed after they are resolved?</t>
+          <t>How quickly will customers be notified of a security incident that affects their data?</t>
         </is>
       </c>
       <c r="C135" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
@@ -11287,7 +11307,7 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>8. Post-incident review</t>
+          <t>7. Customer notification</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -11297,26 +11317,26 @@
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>Every SEV1 and SEV2 incident gets a written post-incident review within 10 business days, covering the root cause and follow-up actions. All incidents, whatever their severity, are recorded in the incident register.</t>
+          <t>If a security incident affects customer data, Quarterhour notifies the affected customers without undue delay and no later than 72 hours after confirming the incident. The notice explains what happened, which data was involved, what we are doing about it and who to contact.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>IR-005</t>
+          <t>IR-003</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Are security incidents recorded and reviewed after they are resolved?</t>
+          <t>Who leads incident response, and are roles defined?</t>
         </is>
       </c>
       <c r="C136" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>0.27</v>
+        <v>0.48</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
@@ -11325,7 +11345,7 @@
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>6. Response steps</t>
+          <t>4. Roles</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -11335,64 +11355,64 @@
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>Preserve evidence: keep relevant logs and snapshots until the post-incident review is complete.</t>
+          <t>Incident Lead: the CTO (backup: the on-call senior engineer). Runs the response and makes technical decisions. • Communications Lead: the CEO. Approves all messages to customers, regulators and partners. • Responders: engineers assigned by the Incident Lead.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>IR-005</t>
+          <t>IR-003</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Are security incidents recorded and reviewed after they are resolved?</t>
+          <t>Who leads incident response, and are roles defined?</t>
         </is>
       </c>
       <c r="C137" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>1. Purpose</t>
+          <t>9. Roles (page 2)</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>business-continuity-plan.pdf</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
+          <t>The CTO leads recovery. The CEO leads communication with customers.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>IR-006</t>
+          <t>IR-003</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>How can customers and security researchers report a security issue?</t>
+          <t>Who leads incident response, and are roles defined?</t>
         </is>
       </c>
       <c r="C138" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
@@ -11401,7 +11421,7 @@
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>5. Detection and reporting</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -11411,28 +11431,26 @@
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>Security alerts from AWS GuardDuty, AWS CloudTrail, application error monitoring and uptime checks go to the on-call engineer. Employees must report a suspected incident straight away in the #security Slack channel or by email to security@quarterhour.example. Customers and security researchers can report vulnerabilities to the same address.</t>
+          <t>Incident Response Plan v1.1. This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>IR-006</t>
+          <t>IR-004</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>How can customers and security researchers report a security issue?</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+          <t>Is the incident response plan tested at least once a year?</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>0.11</v>
+        <v>0.5</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
@@ -11441,7 +11459,7 @@
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>3. Severity levels</t>
+          <t>9. Testing</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -11451,106 +11469,102 @@
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>SEV1: confirmed or likely exposure of customer data, or the service is down for all customers. • SEV2: a limited security issue or a partial outage. • SEV3: a suspicious event with no confirmed impact.</t>
+          <t>This plan is tested with a tabletop exercise at least once a year. The results and any improvements are recorded.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>IR-006</t>
+          <t>IR-004</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>How can customers and security researchers report a security issue?</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+          <t>Is the incident response plan tested at least once a year?</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>7. Vulnerability remediation</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>Vulnerabilities found by scanning, testing or outside reports are fixed within these times after they are confirmed:</t>
+          <t>Incident Response Plan v1.1. This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>IR-007</t>
+          <t>IR-004</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Has the company had a security breach affecting customer data in the past three years?</t>
+          <t>Is the incident response plan tested at least once a year?</t>
         </is>
       </c>
       <c r="C141" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>7. Customer notification</t>
+          <t>8. Testing (page 2)</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>business-continuity-plan.pdf</t>
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>If a security incident affects customer data, Quarterhour notifies the affected customers without undue delay and no later than 72 hours after confirming the incident. The notice explains what happened, which data was involved, what we are doing about it and who to contact.</t>
+          <t>The disaster recovery procedure is tested at least once a year by restoring the service in us-west-2. This plan is reviewed every year and after each major incident.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>IR-007</t>
+          <t>IR-005</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Has the company had a security breach affecting customer data in the past three years?</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+          <t>Are security incidents recorded and reviewed after they are resolved?</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
@@ -11559,7 +11573,7 @@
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>5. Detection and reporting</t>
+          <t>8. Post-incident review</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -11569,28 +11583,26 @@
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>Security alerts from AWS GuardDuty, AWS CloudTrail, application error monitoring and uptime checks go to the on-call engineer. Employees must report a suspected incident straight away in the #security Slack channel or by email to security@quarterhour.example. Customers and security researchers can report vulnerabilities to the same address.</t>
+          <t>Every SEV1 and SEV2 incident gets a written post-incident review within 10 business days, covering the root cause and follow-up actions. All incidents, whatever their severity, are recorded in the incident register.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>IR-007</t>
+          <t>IR-005</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Has the company had a security breach affecting customer data in the past three years?</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+          <t>Are security incidents recorded and reviewed after they are resolved?</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>0.08</v>
+        <v>0.27</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
@@ -11599,7 +11611,7 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>1. Purpose</t>
+          <t>6. Response steps</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -11609,334 +11621,338 @@
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
+          <t>Preserve evidence: keep relevant logs and snapshots until the post-incident review is complete.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>VEN-001</t>
+          <t>IR-005</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Does the company assess the security of vendors before giving them access to data?</t>
+          <t>Are security incidents recorded and reviewed after they are resolved?</t>
         </is>
       </c>
       <c r="C144" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>0.3</v>
+        <v>0.14</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>3. Assessment before use</t>
+          <t>1. Purpose</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire;</t>
+          <t>This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>VEN-001</t>
+          <t>IR-006</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Does the company assess the security of vendors before giving them access to data?</t>
+          <t>How can customers and security researchers report a security issue?</t>
         </is>
       </c>
       <c r="C145" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>5. Ongoing review</t>
+          <t>5. Detection and reporting</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>High-risk vendors are reviewed every year, including their latest security report. Other vendors are reviewed when their contract renews.</t>
+          <t>Security alerts from AWS GuardDuty, AWS CloudTrail, application error monitoring and uptime checks go to the on-call engineer. Employees must report a suspected incident straight away in the #security Slack channel or by email to security@quarterhour.example. Customers and security researchers can report vulnerabilities to the same address.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>VEN-001</t>
+          <t>IR-006</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Does the company assess the security of vendors before giving them access to data?</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="n">
-        <v>3</v>
+          <t>How can customers and security researchers report a security issue?</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>2 (weak)</t>
+        </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>7. Key vendors</t>
+          <t>3. Severity levels</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
+          <t>SEV1: confirmed or likely exposure of customer data, or the service is down for all customers. • SEV2: a limited security issue or a partial outage. • SEV3: a suspicious event with no confirmed impact.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>VEN-002</t>
+          <t>IR-006</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Does the company keep a list of vendors and subprocessors that handle customer data?</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="n">
-        <v>1</v>
+          <t>How can customers and security researchers report a security issue?</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D147" s="3" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>2. Vendor register</t>
+          <t>7. Vulnerability remediation</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>Quarterhour keeps a register of vendors that store or process company or customer data. For each vendor it records the data involved, the risk level and the contract owner. Vendors that process customer personal data are also listed as subprocessors on the public subprocessor list.</t>
+          <t>Vulnerabilities found by scanning, testing or outside reports are fixed within these times after they are confirmed:</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>VEN-002</t>
+          <t>IR-007</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Does the company keep a list of vendors and subprocessors that handle customer data?</t>
+          <t>Has the company had a security breach affecting customer data in the past three years?</t>
         </is>
       </c>
       <c r="C148" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>6. Subprocessor changes</t>
+          <t>7. Customer notification</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>Customers are told at least 30 days before a new subprocessor starts processing their personal data. Notice is sent by email to customer account administrators and the public subprocessor list is updated.</t>
+          <t>If a security incident affects customer data, Quarterhour notifies the affected customers without undue delay and no later than 72 hours after confirming the incident. The notice explains what happened, which data was involved, what we are doing about it and who to contact.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>VEN-002</t>
+          <t>IR-007</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Does the company keep a list of vendors and subprocessors that handle customer data?</t>
+          <t>Has the company had a security breach affecting customer data in the past three years?</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>3. Assessment before use</t>
+          <t>5. Detection and reporting</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>Before a new vendor receives customer data: • the contract owner completes a vendor risk review; • for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire; • a data processing agreement is signed if the vendor will process personal data. • The CTO approves every high-risk vendor.</t>
+          <t>Security alerts from AWS GuardDuty, AWS CloudTrail, application error monitoring and uptime checks go to the on-call engineer. Employees must report a suspected incident straight away in the #security Slack channel or by email to security@quarterhour.example. Customers and security researchers can report vulnerabilities to the same address.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>VEN-003</t>
+          <t>IR-007</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>How often are critical vendors reviewed?</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="n">
-        <v>1</v>
+          <t>Has the company had a security breach affecting customer data in the past three years?</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>5. Ongoing review</t>
+          <t>1. Purpose</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>High-risk vendors are reviewed every year, including their latest security report. Other vendors are reviewed when their contract renews.</t>
+          <t>This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>VEN-003</t>
+          <t>VEN-001</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>How often are critical vendors reviewed?</t>
+          <t>Does the company assess the security of vendors before giving them access to data?</t>
         </is>
       </c>
       <c r="C151" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>8. Testing (page 2)</t>
+          <t>3. Assessment before use</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>business-continuity-plan.pdf</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>The disaster recovery procedure is tested at least once a year by restoring the service in us-west-2. This plan is reviewed every year and after each major incident.</t>
+          <t>for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire;</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>VEN-003</t>
+          <t>VEN-001</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>How often are critical vendors reviewed?</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+          <t>Does the company assess the security of vendors before giving them access to data?</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>0.11</v>
+        <v>0.18</v>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
@@ -11945,7 +11961,7 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>(start of document)</t>
+          <t>5. Ongoing review</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
@@ -11955,26 +11971,26 @@
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>FICTIONAL SAMPLE. Quarterhour, Inc. is a made-up company used to demonstrate this kit. • Document ID: QH-POL-09 • Version: 1.0 • Owner: Dana Whitfield, CTO • Approved by: Maya Okafor, CEO • Last reviewed: 20 May 2026 • Review cycle: at least annually</t>
+          <t>High-risk vendors are reviewed every year, including their latest security report. Other vendors are reviewed when their contract renews.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>VEN-004</t>
+          <t>VEN-001</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Do vendor contracts include security and confidentiality requirements?</t>
+          <t>Does the company assess the security of vendors before giving them access to data?</t>
         </is>
       </c>
       <c r="C153" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>0.63</v>
+        <v>0.13</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
@@ -11983,7 +11999,7 @@
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>4. Contracts</t>
+          <t>7. Key vendors</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -11993,68 +12009,64 @@
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>Vendor contracts must include confidentiality obligations and security requirements, plus data protection terms where personal data is involved.</t>
+          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>VEN-004</t>
+          <t>VEN-002</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Do vendor contracts include security and confidentiality requirements?</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+          <t>Does the company keep a list of vendors and subprocessors that handle customer data?</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>1. Purpose</t>
+          <t>2. Vendor register</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
+          <t>Quarterhour keeps a register of vendors that store or process company or customer data. For each vendor it records the data involved, the risk level and the contract owner. Vendors that process customer personal data are also listed as subprocessors on the public subprocessor list.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>VEN-004</t>
+          <t>VEN-002</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Do vendor contracts include security and confidentiality requirements?</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+          <t>Does the company keep a list of vendors and subprocessors that handle customer data?</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
@@ -12063,7 +12075,7 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>3. Assessment before use</t>
+          <t>6. Subprocessor changes</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -12073,26 +12085,28 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>Before a new vendor receives customer data: • the contract owner completes a vendor risk review; • for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire; • a data processing agreement is signed if the vendor will process personal data. • The CTO approves every high-risk vendor.</t>
+          <t>Customers are told at least 30 days before a new subprocessor starts processing their personal data. Notice is sent by email to customer account administrators and the public subprocessor list is updated.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>VEN-005</t>
+          <t>VEN-002</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Are customers told before a new subprocessor is added?</t>
-        </is>
-      </c>
-      <c r="C156" s="3" t="n">
-        <v>1</v>
+          <t>Does the company keep a list of vendors and subprocessors that handle customer data?</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>0.38</v>
+        <v>0.08</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
@@ -12101,7 +12115,7 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>6. Subprocessor changes</t>
+          <t>3. Assessment before use</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -12111,186 +12125,182 @@
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>Customers are told at least 30 days before a new subprocessor starts processing their personal data. Notice is sent by email to customer account administrators and the public subprocessor list is updated.</t>
+          <t>Before a new vendor receives customer data: • the contract owner completes a vendor risk review; • for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire; • a data processing agreement is signed if the vendor will process personal data. • The CTO approves every high-risk vendor.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>VEN-005</t>
+          <t>VEN-003</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Are customers told before a new subprocessor is added?</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+          <t>How often are critical vendors reviewed?</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>0.12</v>
+        <v>0.39</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>7. Vulnerability remediation</t>
+          <t>5. Ongoing review</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>Vulnerabilities found by scanning, testing or outside reports are fixed within these times after they are confirmed: • Critical: 7 days • High: 30 days • Medium: 90 days • Low: at the next planned update</t>
+          <t>High-risk vendors are reviewed every year, including their latest security report. Other vendors are reviewed when their contract renews.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>VEN-005</t>
+          <t>VEN-003</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Are customers told before a new subprocessor is added?</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+          <t>How often are critical vendors reviewed?</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>2. Vendor register</t>
+          <t>8. Testing (page 2)</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>business-continuity-plan.pdf</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>Quarterhour keeps a register of vendors that store or process company or customer data. For each vendor it records the data involved, the risk level and the contract owner. Vendors that process customer personal data are also listed as subprocessors on the public subprocessor list.</t>
+          <t>The disaster recovery procedure is tested at least once a year by restoring the service in us-west-2. This plan is reviewed every year and after each major incident.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>SDL-001</t>
+          <t>VEN-003</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Does the company follow a documented secure development process?</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="n">
-        <v>1</v>
+          <t>How often are critical vendors reviewed?</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>0.37</v>
+        <v>0.11</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>(start of document)</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2. To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
+          <t>FICTIONAL SAMPLE. Quarterhour, Inc. is a made-up company used to demonstrate this kit. • Document ID: QH-POL-09 • Version: 1.0 • Owner: Dana Whitfield, CTO • Approved by: Maya Okafor, CEO • Last reviewed: 20 May 2026 • Review cycle: at least annually</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>SDL-001</t>
+          <t>VEN-004</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Does the company follow a documented secure development process?</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+          <t>Do vendor contracts include security and confidentiality requirements?</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>0.1</v>
+        <v>0.66</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>1. Purpose</t>
+          <t>4. Contracts</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
+          <t>Vendor contracts must include confidentiality obligations and security requirements, plus data protection terms where personal data is involved.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>SDL-001</t>
+          <t>VEN-004</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Does the company follow a documented secure development process?</t>
+          <t>Do vendor contracts include security and confidentiality requirements?</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
@@ -12299,7 +12309,7 @@
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>3. Assessment before use</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -12309,99 +12319,103 @@
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0. To manage the security risk of third parties that store or process Quarterhour or customer data.</t>
+          <t>Before a new vendor receives customer data: • the contract owner completes a vendor risk review; • for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire; • a data processing agreement is signed if the vendor will process personal data. • The CTO approves every high-risk vendor.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>SDL-002</t>
+          <t>VEN-004</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Is every code change reviewed by another person before it is deployed?</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="n">
-        <v>1</v>
+          <t>Do vendor contracts include security and confidentiality requirements?</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>3. Code review</t>
+          <t>5. Ongoing review</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>Every change is made through a pull request and needs at least one approving review from an engineer other than the author before it can be merged.</t>
+          <t>High-risk vendors are reviewed every year, including their latest security report. Other vendors are reviewed when their contract renews.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>SDL-002</t>
+          <t>VEN-005</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Is every code change reviewed by another person before it is deployed?</t>
+          <t>Are customers told before a new subprocessor is added?</t>
         </is>
       </c>
       <c r="C163" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>6. Deployment and change management</t>
+          <t>6. Subprocessor changes</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>Only code merged to the main branch can be deployed to production, and only through the automated CI/CD pipeline. Each deployment is logged with the changes it contains. A failed deployment is rolled back to the previous version. Infrastructure is defined as code and changes to it are reviewed the same way as application code.</t>
+          <t>Customers are told at least 30 days before a new subprocessor starts processing their personal data. Notice is sent by email to customer account administrators and the public subprocessor list is updated.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>SDL-002</t>
+          <t>VEN-005</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Is every code change reviewed by another person before it is deployed?</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="n">
-        <v>3</v>
+          <t>Are customers told before a new subprocessor is added?</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>2 (weak)</t>
+        </is>
       </c>
       <c r="D164" s="3" t="n">
         <v>0.12</v>
@@ -12413,7 +12427,7 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>4. Automated checks</t>
+          <t>7. Vulnerability remediation</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -12423,100 +12437,102 @@
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>Every pull request runs automated tests, static code analysis for common security flaws, and dependency scanning for known vulnerable packages. Secret scanning is turned on for all repositories. A pull request cannot be merged while a required check is failing.</t>
+          <t>Vulnerabilities found by scanning, testing or outside reports are fixed within these times after they are confirmed: • Critical: 7 days • High: 30 days • Medium: 90 days • Low: at the next planned update</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>SDL-003</t>
+          <t>VEN-005</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Are development, test and production environments kept separate?</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="n">
-        <v>1</v>
+          <t>Are customers told before a new subprocessor is added?</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>0.54</v>
+        <v>0.11</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>5. Environments</t>
+          <t>2. Vendor register</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>Development, staging and production are separate. Staging and production run in separate AWS accounts. Production customer data is never copied to development or staging; those environments use synthetic test data.</t>
+          <t>Quarterhour keeps a register of vendors that store or process company or customer data. For each vendor it records the data involved, the risk level and the contract owner. Vendors that process customer personal data are also listed as subprocessors on the public subprocessor list.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>SDL-003</t>
+          <t>SDL-001</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Are development, test and production environments kept separate?</t>
+          <t>Does the company follow a documented secure development process?</t>
         </is>
       </c>
       <c r="C166" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>0.14</v>
+        <v>0.37</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>5. Backup location</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>Backups are copied to the AWS us-west-2 region (United States), into a separate AWS account that is used only for backups.</t>
+          <t>Secure Development Policy v1.2. To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>SDL-003</t>
+          <t>SDL-001</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Are development, test and production environments kept separate?</t>
+          <t>Does the company follow a documented secure development process?</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D167" s="3" t="n">
@@ -12524,117 +12540,119 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>5.1 Production administrators</t>
+          <t>1. Purpose</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>Administrator access to the production AWS account is limited to the CTO and two named senior engineers. The current list is kept in the access register.</t>
+          <t>To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>SDL-004</t>
+          <t>SDL-001</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Is automated security testing run on code (static analysis, dependency scanning)?</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="n">
-        <v>1</v>
+          <t>Does the company follow a documented secure development process?</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>0.26</v>
+        <v>0.09</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>4. Automated checks</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>Every pull request runs automated tests, static code analysis for common security flaws, and dependency scanning for known vulnerable packages. Secret scanning is turned on for all repositories. A pull request cannot be merged while a required check is failing.</t>
+          <t>Vendor Management Policy v1.0. To manage the security risk of third parties that store or process Quarterhour or customer data.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>SDL-004</t>
+          <t>SDL-002</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Is automated security testing run on code (static analysis, dependency scanning)?</t>
+          <t>Is every code change reviewed by another person before it is deployed?</t>
         </is>
       </c>
       <c r="C169" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>5. Application secrets</t>
+          <t>3. Code review</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>API keys, database passwords and other secrets are stored in AWS Secrets Manager. Secrets must never be committed to source code. Secret scanning is turned on for all code repositories.</t>
+          <t>Every change is made through a pull request and needs at least one approving review from an engineer other than the author before it can be merged.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>SDL-004</t>
+          <t>SDL-002</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Is automated security testing run on code (static analysis, dependency scanning)?</t>
+          <t>Is every code change reviewed by another person before it is deployed?</t>
         </is>
       </c>
       <c r="C170" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -12643,7 +12661,7 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>1. Purpose</t>
+          <t>6. Deployment and change management</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -12653,26 +12671,26 @@
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
+          <t>Only code merged to the main branch can be deployed to production, and only through the automated CI/CD pipeline. Each deployment is logged with the changes it contains. A failed deployment is rolled back to the previous version. Infrastructure is defined as code and changes to it are reviewed the same way as application code.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>SDL-005</t>
+          <t>SDL-002</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>How are changes to production approved, deployed and rolled back?</t>
+          <t>Is every code change reviewed by another person before it is deployed?</t>
         </is>
       </c>
       <c r="C171" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -12681,7 +12699,7 @@
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>6. Deployment and change management</t>
+          <t>4. Automated checks</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -12691,26 +12709,26 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>Only code merged to the main branch can be deployed to production, and only through the automated CI/CD pipeline. Each deployment is logged with the changes it contains. A failed deployment is rolled back to the previous version. Infrastructure is defined as code and changes to it are reviewed the same way as application code.</t>
+          <t>Every pull request runs automated tests, static code analysis for common security flaws, and dependency scanning for known vulnerable packages. Secret scanning is turned on for all repositories. A pull request cannot be merged while a required check is failing.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>SDL-006</t>
+          <t>SDL-003</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Do developers receive secure coding training?</t>
+          <t>Are development, test and production environments kept separate?</t>
         </is>
       </c>
       <c r="C172" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>0.59</v>
+        <v>0.54</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -12719,7 +12737,7 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>9. Training</t>
+          <t>5. Environments</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -12729,106 +12747,102 @@
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>Engineers complete secure coding training based on the OWASP Top 10 when they join and every year after that.</t>
+          <t>Development, staging and production are separate. Staging and production run in separate AWS accounts. Production customer data is never copied to development or staging; those environments use synthetic test data.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>SDL-006</t>
+          <t>SDL-003</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Do developers receive secure coding training?</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+          <t>Are development, test and production environments kept separate?</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>5. Backup location</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2. To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
+          <t>Backups are copied to the AWS us-west-2 region (United States), into a separate AWS account that is used only for backups.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>SDL-007</t>
+          <t>SDL-003</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>How are open-source and third-party software components kept up to date?</t>
+          <t>Are development, test and production environments kept separate?</t>
         </is>
       </c>
       <c r="C174" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>0.36</v>
+        <v>0.14</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>10. Third-party components</t>
+          <t>8. Restore testing</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>New open-source dependencies are added through pull requests. Automated update requests keep dependencies current. Dependencies with known critical vulnerabilities are not allowed in production.</t>
+          <t>Every quarter, engineering restores the production database from backup into an isolated test environment, checks that the data is complete, and records the result and the time taken. The restored copy is deleted after the test.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>SDL-007</t>
+          <t>SDL-004</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>How are open-source and third-party software components kept up to date?</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+          <t>Is automated security testing run on code (static analysis, dependency scanning)?</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
@@ -12854,59 +12868,57 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>SDL-007</t>
+          <t>SDL-004</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>How are open-source and third-party software components kept up to date?</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+          <t>Is automated security testing run on code (static analysis, dependency scanning)?</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Encryption and Key Management Standard v1.1</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>7. Vulnerability remediation</t>
+          <t>5. Application secrets</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>encryption-standard.docx</t>
         </is>
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>Vulnerabilities found by scanning, testing or outside reports are fixed within these times after they are confirmed: • Critical: 7 days • High: 30 days • Medium: 90 days • Low: at the next planned update</t>
+          <t>API keys, database passwords and other secrets are stored in AWS Secrets Manager. Secrets must never be committed to source code. Secret scanning is turned on for all code repositories.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>SDL-008</t>
+          <t>SDL-004</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>How is access to source code controlled?</t>
+          <t>Is automated security testing run on code (static analysis, dependency scanning)?</t>
         </is>
       </c>
       <c r="C177" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -12915,7 +12927,7 @@
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>2. Source code</t>
+          <t>1. Purpose</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -12925,102 +12937,104 @@
       </c>
       <c r="H177" s="3" t="inlineStr">
         <is>
-          <t>All code is stored in private GitHub repositories. Engineers use individual accounts with MFA. The main branch is protected, so nobody can push to it directly.</t>
+          <t>To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>SDL-008</t>
+          <t>SDL-005</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>How is access to source code controlled?</t>
+          <t>How are changes to production approved, deployed and rolled back?</t>
         </is>
       </c>
       <c r="C178" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>0.22</v>
+        <v>0.5</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>7. Key vendors</t>
+          <t>6. Deployment and change management</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H178" s="3" t="inlineStr">
         <is>
-          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
+          <t>Only code merged to the main branch can be deployed to production, and only through the automated CI/CD pipeline. Each deployment is logged with the changes it contains. A failed deployment is rolled back to the previous version. Infrastructure is defined as code and changes to it are reviewed the same way as application code.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>SDL-008</t>
+          <t>SDL-006</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>How is access to source code controlled?</t>
+          <t>Do developers receive secure coding training?</t>
         </is>
       </c>
       <c r="C179" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>0.21</v>
+        <v>0.59</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>5. Application secrets</t>
+          <t>9. Training</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H179" s="3" t="inlineStr">
         <is>
-          <t>API keys, database passwords and other secrets are stored in AWS Secrets Manager. Secrets must never be committed to source code. Secret scanning is turned on for all code repositories.</t>
+          <t>Engineers complete secure coding training based on the OWASP Top 10 when they join and every year after that.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>VUL-001</t>
+          <t>SDL-006</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Is an independent penetration test performed at least once a year?</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="n">
-        <v>1</v>
+          <t>Do developers receive secure coding training?</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>2 (weak)</t>
+        </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>0.42</v>
+        <v>0.1</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
@@ -13029,7 +13043,7 @@
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>8. Penetration testing</t>
+          <t>(whole document)</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -13039,104 +13053,106 @@
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>An independent third party performs a penetration test of the Quarterhour application and its public infrastructure at least once a year. Findings are fixed within the times in section 7.</t>
+          <t>Secure Development Policy v1.2. To make sure security is part of how Quarterhour designs, builds, tests and releases software.</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>VUL-001</t>
+          <t>SDL-007</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Is an independent penetration test performed at least once a year?</t>
+          <t>How are open-source and third-party software components kept up to date?</t>
         </is>
       </c>
       <c r="C181" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>0.13</v>
+        <v>0.36</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>8. Testing (page 2)</t>
+          <t>10. Third-party components</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>business-continuity-plan.pdf</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>The disaster recovery procedure is tested at least once a year by restoring the service in us-west-2. This plan is reviewed every year and after each major incident.</t>
+          <t>New open-source dependencies are added through pull requests. Automated update requests keep dependencies current. Dependencies with known critical vulnerabilities are not allowed in production.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>VUL-001</t>
+          <t>SDL-007</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Is an independent penetration test performed at least once a year?</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="n">
-        <v>3</v>
+          <t>How are open-source and third-party software components kept up to date?</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>2 (weak)</t>
+        </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>9. Testing</t>
+          <t>4. Automated checks</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H182" s="3" t="inlineStr">
         <is>
-          <t>This plan is tested with a tabletop exercise at least once a year. The results and any improvements are recorded.</t>
+          <t>Every pull request runs automated tests, static code analysis for common security flaws, and dependency scanning for known vulnerable packages. Secret scanning is turned on for all repositories. A pull request cannot be merged while a required check is failing.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>VUL-002</t>
+          <t>SDL-007</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Are systems and infrastructure scanned for vulnerabilities regularly?</t>
+          <t>How are open-source and third-party software components kept up to date?</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
         <is>
-          <t>1 (weak)</t>
+          <t>3 (weak)</t>
         </is>
       </c>
       <c r="D183" s="3" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
@@ -13155,28 +13171,26 @@
       </c>
       <c r="H183" s="3" t="inlineStr">
         <is>
-          <t>Vulnerabilities found by scanning, testing or outside reports are fixed within these times after they are confirmed:</t>
+          <t>Vulnerabilities found by scanning, testing or outside reports are fixed within these times after they are confirmed: • Critical: 7 days • High: 30 days • Medium: 90 days • Low: at the next planned update</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>VUL-002</t>
+          <t>SDL-008</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Are systems and infrastructure scanned for vulnerabilities regularly?</t>
-        </is>
-      </c>
-      <c r="C184" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+          <t>How is access to source code controlled?</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
@@ -13185,7 +13199,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>8. Penetration testing</t>
+          <t>2. Source code</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -13195,217 +13209,209 @@
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>An independent third party performs a penetration test of the Quarterhour application and its public infrastructure at least once a year. Findings are fixed within the times in section 7.</t>
+          <t>All code is stored in private GitHub repositories. Engineers use individual accounts with MFA. The main branch is protected, so nobody can push to it directly.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>VUL-002</t>
+          <t>SDL-008</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Are systems and infrastructure scanned for vulnerabilities regularly?</t>
-        </is>
-      </c>
-      <c r="C185" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+          <t>How is access to source code controlled?</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>4. Automated checks</t>
+          <t>7. Key vendors</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H185" s="3" t="inlineStr">
         <is>
-          <t>Every pull request runs automated tests, static code analysis for common security flaws, and dependency scanning for known vulnerable packages. Secret scanning is turned on for all repositories. A pull request cannot be merged while a required check is failing.</t>
+          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>VUL-003</t>
+          <t>SDL-008</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>How quickly are vulnerabilities fixed, by severity?</t>
+          <t>How is access to source code controlled?</t>
         </is>
       </c>
       <c r="C186" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Encryption and Key Management Standard v1.1</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>7. Vulnerability remediation</t>
+          <t>5. Application secrets</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>encryption-standard.docx</t>
         </is>
       </c>
       <c r="H186" s="3" t="inlineStr">
         <is>
-          <t>Vulnerabilities found by scanning, testing or outside reports are fixed within these times after they are confirmed: • Critical: 7 days • High: 30 days • Medium: 90 days • Low: at the next planned update</t>
+          <t>API keys, database passwords and other secrets are stored in AWS Secrets Manager. Secrets must never be committed to source code. Secret scanning is turned on for all code repositories.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>VUL-003</t>
+          <t>VUL-001</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>How quickly are vulnerabilities fixed, by severity?</t>
-        </is>
-      </c>
-      <c r="C187" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+          <t>Is an independent penetration test performed at least once a year?</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>0.1</v>
+        <v>0.42</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>3. Assessment before use</t>
+          <t>8. Penetration testing</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H187" s="3" t="inlineStr">
         <is>
-          <t>Before a new vendor receives customer data: • the contract owner completes a vendor risk review; • for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire; • a data processing agreement is signed if the vendor will process personal data. • The CTO approves every high-risk vendor.</t>
+          <t>An independent third party performs a penetration test of the Quarterhour application and its public infrastructure at least once a year. Findings are fixed within the times in section 7.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>VUL-003</t>
+          <t>VUL-001</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>How quickly are vulnerabilities fixed, by severity?</t>
-        </is>
-      </c>
-      <c r="C188" s="3" t="inlineStr">
-        <is>
-          <t>3 (weak)</t>
-        </is>
+          <t>Is an independent penetration test performed at least once a year?</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>7. Key vendors</t>
+          <t>8. Testing (page 2)</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>business-continuity-plan.pdf</t>
         </is>
       </c>
       <c r="H188" s="3" t="inlineStr">
         <is>
-          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
+          <t>The disaster recovery procedure is tested at least once a year by restoring the service in us-west-2. This plan is reviewed every year and after each major incident.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>VUL-004</t>
+          <t>VUL-001</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>How are operating systems and infrastructure patched?</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="inlineStr">
-        <is>
-          <t>1 (weak)</t>
-        </is>
+          <t>Is an independent penetration test performed at least once a year?</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>8. Remote access</t>
+          <t>9. Testing</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>Quarterhour does not operate a corporate office network or VPN. Production servers are not reachable over SSH from the internet. Engineers connect through AWS Systems Manager Session Manager using their individual, MFA-protected identities.</t>
+          <t>This plan is tested with a tabletop exercise at least once a year. The results and any improvements are recorded.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>LOG-001</t>
+          <t>VUL-002</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Are security-relevant events logged?</t>
+          <t>Are systems and infrastructure scanned for vulnerabilities regularly?</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -13414,38 +13420,38 @@
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>3. Severity levels</t>
+          <t>7. Vulnerability remediation</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
-          <t>SEV1: confirmed or likely exposure of customer data, or the service is down for all customers. • SEV2: a limited security issue or a partial outage. • SEV3: a suspicious event with no confirmed impact.</t>
+          <t>Vulnerabilities found by scanning, testing or outside reports are fixed within these times after they are confirmed:</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>LOG-001</t>
+          <t>VUL-002</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>Are security-relevant events logged?</t>
+          <t>Are systems and infrastructure scanned for vulnerabilities regularly?</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -13454,38 +13460,38 @@
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>6. Response steps</t>
+          <t>8. Penetration testing</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
-          <t>Preserve evidence: keep relevant logs and snapshots until the post-incident review is complete.</t>
+          <t>An independent third party performs a penetration test of the Quarterhour application and its public infrastructure at least once a year. Findings are fixed within the times in section 7.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>LOG-001</t>
+          <t>VUL-002</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Are security-relevant events logged?</t>
+          <t>Are systems and infrastructure scanned for vulnerabilities regularly?</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -13498,110 +13504,112 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>2. What counts as a security incident</t>
+          <t>4. Automated checks</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
-          <t>Any event that threatens the confidentiality, integrity or availability of customer data or Quarterhour systems. Examples: unauthorised access, exposure of customer data, malware on a company device, or a compromised account.</t>
+          <t>Every pull request runs automated tests, static code analysis for common security flaws, and dependency scanning for known vulnerable packages. Secret scanning is turned on for all repositories. A pull request cannot be merged while a required check is failing.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>LOG-002</t>
+          <t>VUL-003</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>How long are security logs kept?</t>
+          <t>How quickly are vulnerabilities fixed, by severity?</t>
         </is>
       </c>
       <c r="C193" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Secure Development Policy v1.2</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>4. Retention</t>
+          <t>7. Vulnerability remediation</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>secure-development-policy.md</t>
         </is>
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>Automated database backups are kept for 35 days. • One snapshot a month is kept for 12 months. • Previous versions of S3 objects are kept for 35 days.</t>
+          <t>Vulnerabilities found by scanning, testing or outside reports are fixed within these times after they are confirmed: • Critical: 7 days • High: 30 days • Medium: 90 days • Low: at the next planned update</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>LOG-002</t>
+          <t>VUL-003</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>How long are security logs kept?</t>
-        </is>
-      </c>
-      <c r="C194" s="3" t="n">
-        <v>2</v>
+          <t>How quickly are vulnerabilities fixed, by severity?</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>2 (weak)</t>
+        </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>3. Backup frequency</t>
+          <t>3. Assessment before use</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>Amazon RDS takes an automated snapshot of the production database every day and keeps transaction logs for point-in-time recovery. The database can be restored to any point within the retention period, normally to within 5 minutes.</t>
+          <t>Before a new vendor receives customer data: • the contract owner completes a vendor risk review; • for high-risk vendors (those that store or process customer data), Quarterhour reviews the vendor's SOC 2 report, ISO 27001 certificate or completed security questionnaire; • a data processing agreement is signed if the vendor will process personal data. • The CTO approves every high-risk vendor.</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>LOG-002</t>
+          <t>VUL-003</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>How long are security logs kept?</t>
+          <t>How quickly are vulnerabilities fixed, by severity?</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -13610,81 +13618,83 @@
         </is>
       </c>
       <c r="D195" s="3" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Backup and Recovery Policy v1.2</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>7. Access to backups</t>
+          <t>7. Key vendors</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>backup-and-recovery-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>Only the CTO and one named senior engineer can restore or delete backups. The backup account blocks deletion of snapshots before the end of their retention period.</t>
+          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>LOG-003</t>
+          <t>VUL-004</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Are logs and alerts monitored for suspicious activity?</t>
-        </is>
-      </c>
-      <c r="C196" s="3" t="n">
-        <v>1</v>
+          <t>How are operating systems and infrastructure patched?</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>1 (weak)</t>
+        </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Incident Response Plan v1.1</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>5. Detection and reporting</t>
+          <t>8. Remote access</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>incident-response-plan.md</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H196" s="3" t="inlineStr">
         <is>
-          <t>Security alerts from AWS GuardDuty, AWS CloudTrail, application error monitoring and uptime checks go to the on-call engineer. Employees must report a suspected incident straight away in the #security Slack channel or by email to security@quarterhour.example. Customers and security researchers can report vulnerabilities to the same address.</t>
+          <t>Quarterhour does not operate a corporate office network or VPN. Production servers are not reachable over SSH from the internet. Engineers connect through AWS Systems Manager Session Manager using their individual, MFA-protected identities.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>LOG-003</t>
+          <t>LOG-001</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Are logs and alerts monitored for suspicious activity?</t>
+          <t>Are security-relevant events logged?</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>2 (weak)</t>
+          <t>1 (weak)</t>
         </is>
       </c>
       <c r="D197" s="3" t="n">
@@ -13697,7 +13707,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>1. Purpose</t>
+          <t>3. Severity levels</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -13707,28 +13717,28 @@
       </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
-          <t>This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
+          <t>SEV1: confirmed or likely exposure of customer data, or the service is down for all customers. • SEV2: a limited security issue or a partial outage. • SEV3: a suspicious event with no confirmed impact.</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>LOG-005</t>
+          <t>LOG-001</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Does the product give customers an audit log of user activity?</t>
+          <t>Are security-relevant events logged?</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>1 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -13754,17 +13764,17 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>LOG-005</t>
+          <t>LOG-001</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Does the product give customers an audit log of user activity?</t>
+          <t>Are security-relevant events logged?</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>2 (weak)</t>
+          <t>3 (weak)</t>
         </is>
       </c>
       <c r="D199" s="3" t="n">
@@ -13772,74 +13782,72 @@
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>2. Scope</t>
+          <t>6. Response steps</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>It applies to all employees and contractors, and to every system that stores or processes Quarterhour or customer data, including AWS, GitHub, Google Workspace, Stripe and the Quarterhour admin console.</t>
+          <t>Preserve evidence: keep relevant logs and snapshots until the post-incident review is complete.</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>NET-001</t>
+          <t>LOG-002</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Which cloud provider hosts the production environment?</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="inlineStr">
-        <is>
-          <t>1 (weak)</t>
-        </is>
+          <t>How long are security logs kept?</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D200" s="3" t="n">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Vendor Management Policy v1.0</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>7. Key vendors</t>
+          <t>4. Retention</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>vendor-management-policy.md</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
-          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
+          <t>Automated database backups are kept for 35 days. • One snapshot a month is kept for 12 months. • Previous versions of S3 objects are kept for 35 days.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>NET-001</t>
+          <t>LOG-002</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Which cloud provider hosts the production environment?</t>
+          <t>How long are security logs kept?</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -13848,165 +13856,165 @@
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Secure Development Policy v1.2</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>5. Environments</t>
+          <t>3. Backup frequency</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>secure-development-policy.md</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>Development, staging and production are separate. Staging and production run in separate AWS accounts. Production customer data is never copied to development or staging; those environments use synthetic test data.</t>
+          <t>Amazon RDS takes an automated snapshot of the production database every day and keeps transaction logs for point-in-time recovery. The database can be restored to any point within the retention period, normally to within 5 minutes.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>NET-002</t>
+          <t>LOG-002</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>How is network access to production systems restricted?</t>
+          <t>How long are security logs kept?</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>1 (weak)</t>
+          <t>3 (weak)</t>
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Backup and Recovery Policy v1.2</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>8. Remote access</t>
+          <t>7. Access to backups</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>backup-and-recovery-policy.md</t>
         </is>
       </c>
       <c r="H202" s="3" t="inlineStr">
         <is>
-          <t>Quarterhour does not operate a corporate office network or VPN. Production servers are not reachable over SSH from the internet. Engineers connect through AWS Systems Manager Session Manager using their individual, MFA-protected identities.</t>
+          <t>Only the CTO and one named senior engineer can restore or delete backups. The backup account blocks deletion of snapshots before the end of their retention period.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>NET-002</t>
+          <t>LOG-003</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>How is network access to production systems restricted?</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="inlineStr">
-        <is>
-          <t>2 (weak)</t>
-        </is>
+          <t>Are logs and alerts monitored for suspicious activity?</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>5.1 Production administrators</t>
+          <t>5. Detection and reporting</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
-          <t>Administrator access to the production AWS account is limited to the CTO and two named senior engineers. The current list is kept in the access register.</t>
+          <t>Security alerts from AWS GuardDuty, AWS CloudTrail, application error monitoring and uptime checks go to the on-call engineer. Employees must report a suspected incident straight away in the #security Slack channel or by email to security@quarterhour.example. Customers and security researchers can report vulnerabilities to the same address.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>NET-002</t>
+          <t>LOG-003</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>How is network access to production systems restricted?</t>
+          <t>Are logs and alerts monitored for suspicious activity?</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Incident Response Plan v1.1</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>5.2 Access to customer data</t>
+          <t>1. Purpose</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>incident-response-plan.md</t>
         </is>
       </c>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>Support staff view customer accounts through the Quarterhour admin console, which limits what each role can see. Direct access to the production database is limited to on-call engineers, goes through AWS Systems Manager Session Manager, and is logged in AWS CloudTrail.</t>
+          <t>This plan describes how Quarterhour detects, responds to and learns from security incidents.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>NET-003</t>
+          <t>LOG-005</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>How do engineers connect to production systems remotely?</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="n">
-        <v>1</v>
+          <t>Does the product give customers an audit log of user activity?</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="inlineStr">
+        <is>
+          <t>1 (weak)</t>
+        </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>0.33</v>
+        <v>0.1</v>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
@@ -14015,7 +14023,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>8. Remote access</t>
+          <t>5.2 Access to customer data</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -14025,19 +14033,19 @@
       </c>
       <c r="H205" s="3" t="inlineStr">
         <is>
-          <t>Quarterhour does not operate a corporate office network or VPN. Production servers are not reachable over SSH from the internet. Engineers connect through AWS Systems Manager Session Manager using their individual, MFA-protected identities.</t>
+          <t>Support staff view customer accounts through the Quarterhour admin console, which limits what each role can see. Direct access to the production database is limited to on-call engineers, goes through AWS Systems Manager Session Manager, and is logged in AWS CloudTrail.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>NET-003</t>
+          <t>LOG-005</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>How do engineers connect to production systems remotely?</t>
+          <t>Does the product give customers an audit log of user activity?</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -14046,7 +14054,7 @@
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
@@ -14055,7 +14063,7 @@
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>5.1 Production administrators</t>
+          <t>2. Scope</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
@@ -14065,68 +14073,68 @@
       </c>
       <c r="H206" s="3" t="inlineStr">
         <is>
-          <t>Administrator access to the production AWS account is limited to the CTO and two named senior engineers. The current list is kept in the access register.</t>
+          <t>It applies to all employees and contractors, and to every system that stores or processes Quarterhour or customer data, including AWS, GitHub, Google Workspace, Stripe and the Quarterhour admin console.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>NET-003</t>
+          <t>NET-001</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>How do engineers connect to production systems remotely?</t>
+          <t>Which cloud provider hosts the production environment?</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>3 (weak)</t>
+          <t>1 (weak)</t>
         </is>
       </c>
       <c r="D207" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>Access Control Policy v1.3</t>
+          <t>Vendor Management Policy v1.0</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>5.2 Access to customer data</t>
+          <t>7. Key vendors</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>access-control-policy.md</t>
+          <t>vendor-management-policy.md</t>
         </is>
       </c>
       <c r="H207" s="3" t="inlineStr">
         <is>
-          <t>Support staff view customer accounts through the Quarterhour admin console, which limits what each role can see. Direct access to the production database is limited to on-call engineers, goes through AWS Systems Manager Session Manager, and is logged in AWS CloudTrail.</t>
+          <t>Amazon Web Services: hosting, database and backups (high risk). • Google Workspace: company email and documents (high risk). • GitHub: source code hosting (medium risk). • Stripe: payment processing (medium risk). Card details are entered on Stripe-hosted payment forms. Quarterhour systems do not store or process full card numbers. • Transactional email and SMS providers: appointment reminders (high risk).</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>NET-005</t>
+          <t>NET-001</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Are servers and cloud resources configured to a hardened baseline?</t>
+          <t>Which cloud provider hosts the production environment?</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>1 (weak)</t>
+          <t>2 (weak)</t>
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -14135,7 +14143,7 @@
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>6. Deployment and change management</t>
+          <t>5. Environments</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -14145,102 +14153,104 @@
       </c>
       <c r="H208" s="3" t="inlineStr">
         <is>
-          <t>Only code merged to the main branch can be deployed to production, and only through the automated CI/CD pipeline. Each deployment is logged with the changes it contains. A failed deployment is rolled back to the previous version. Infrastructure is defined as code and changes to it are reviewed the same way as application code.</t>
+          <t>Development, staging and production are separate. Staging and production run in separate AWS accounts. Production customer data is never copied to development or staging; those environments use synthetic test data.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>NET-005</t>
+          <t>NET-002</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Are servers and cloud resources configured to a hardened baseline?</t>
+          <t>How is network access to production systems restricted?</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>2 (weak)</t>
+          <t>1 (weak)</t>
         </is>
       </c>
       <c r="D209" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>5. Disaster recovery (page 1)</t>
+          <t>5.1 Production administrators</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>business-continuity-plan.pdf</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H209" s="3" t="inlineStr">
         <is>
-          <t>If the us-east-1 region becomes unavailable, the team rebuilds the service in the us-west-2 region from the cross-region backups described in the Backup and Recovery Policy, using infrastructure-as-code templates. The CTO decides when to start regional recovery.</t>
+          <t>Administrator access to the production AWS account is limited to the CTO and two named senior engineers. The current list is kept in the access register.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>END-001</t>
+          <t>NET-002</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Are company laptops encrypted and centrally managed?</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="n">
-        <v>1</v>
+          <t>How is network access to production systems restricted?</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>2 (weak)</t>
+        </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>6. Laptops</t>
+          <t>8. Remote access</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>Company laptops must have full-disk encryption (FileVault) turned on. This is checked through the company's device management (MDM) tool.</t>
+          <t>Quarterhour does not operate a corporate office network or VPN. Production servers are not reachable over SSH from the internet. Engineers connect through AWS Systems Manager Session Manager using their individual, MFA-protected identities.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>END-001</t>
+          <t>NET-002</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Are company laptops encrypted and centrally managed?</t>
+          <t>How is network access to production systems restricted?</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
         <is>
-          <t>2 (weak)</t>
+          <t>3 (weak)</t>
         </is>
       </c>
       <c r="D211" s="3" t="n">
@@ -14248,105 +14258,459 @@
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>(whole document)</t>
+          <t>5.2 Access to customer data</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>encryption-standard.docx</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
+          <t>Support staff view customer accounts through the Quarterhour admin console, which limits what each role can see. Direct access to the production database is limited to on-call engineers, goes through AWS Systems Manager Session Manager, and is logged in AWS CloudTrail.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>PHY-002</t>
+          <t>NET-003</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Does the company have offices where customer data is accessed?</t>
+          <t>How do engineers connect to production systems remotely?</t>
         </is>
       </c>
       <c r="C212" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+          <t>Access Control Policy v1.3</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>6. People and workplace (page 2)</t>
+          <t>8. Remote access</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>business-continuity-plan.pdf</t>
+          <t>access-control-policy.md</t>
         </is>
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>Quarterhour is a remote-first company with no office. Staff can work from any location with internet access, so the loss of a workplace does not stop operations. At least two people can perform each critical task.</t>
+          <t>Quarterhour does not operate a corporate office network or VPN. Production servers are not reachable over SSH from the internet. Engineers connect through AWS Systems Manager Session Manager using their individual, MFA-protected identities.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
+          <t>NET-003</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>How do engineers connect to production systems remotely?</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D213" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
+        <is>
+          <t>Access Control Policy v1.3</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="inlineStr">
+        <is>
+          <t>5.2 Access to customer data</t>
+        </is>
+      </c>
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>access-control-policy.md</t>
+        </is>
+      </c>
+      <c r="H213" s="3" t="inlineStr">
+        <is>
+          <t>Support staff view customer accounts through the Quarterhour admin console, which limits what each role can see. Direct access to the production database is limited to on-call engineers, goes through AWS Systems Manager Session Manager, and is logged in AWS CloudTrail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>NET-003</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>How do engineers connect to production systems remotely?</t>
+        </is>
+      </c>
+      <c r="C214" s="3" t="inlineStr">
+        <is>
+          <t>3 (weak)</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
+        <is>
+          <t>Access Control Policy v1.3</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="inlineStr">
+        <is>
+          <t>5.1 Production administrators</t>
+        </is>
+      </c>
+      <c r="G214" s="3" t="inlineStr">
+        <is>
+          <t>access-control-policy.md</t>
+        </is>
+      </c>
+      <c r="H214" s="3" t="inlineStr">
+        <is>
+          <t>Administrator access to the production AWS account is limited to the CTO and two named senior engineers. The current list is kept in the access register.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>NET-005</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr">
+        <is>
+          <t>Are servers and cloud resources configured to a hardened baseline?</t>
+        </is>
+      </c>
+      <c r="C215" s="3" t="inlineStr">
+        <is>
+          <t>1 (weak)</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>Secure Development Policy v1.2</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>6. Deployment and change management</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>secure-development-policy.md</t>
+        </is>
+      </c>
+      <c r="H215" s="3" t="inlineStr">
+        <is>
+          <t>Only code merged to the main branch can be deployed to production, and only through the automated CI/CD pipeline. Each deployment is logged with the changes it contains. A failed deployment is rolled back to the previous version. Infrastructure is defined as code and changes to it are reviewed the same way as application code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>NET-005</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>Are servers and cloud resources configured to a hardened baseline?</t>
+        </is>
+      </c>
+      <c r="C216" s="3" t="inlineStr">
+        <is>
+          <t>2 (weak)</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>5. Disaster recovery (page 1)</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>business-continuity-plan.pdf</t>
+        </is>
+      </c>
+      <c r="H216" s="3" t="inlineStr">
+        <is>
+          <t>If the us-east-1 region becomes unavailable, the team rebuilds the service in the us-west-2 region from the cross-region backups described in the Backup and Recovery Policy, using infrastructure-as-code templates. The CTO decides when to start regional recovery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>END-001</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr">
+        <is>
+          <t>Are company laptops encrypted and centrally managed?</t>
+        </is>
+      </c>
+      <c r="C217" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>Encryption and Key Management Standard v1.1</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>6. Laptops</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>encryption-standard.docx</t>
+        </is>
+      </c>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>Company laptops must have full-disk encryption (FileVault) turned on. This is checked through the company's device management (MDM) tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>END-001</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>Are company laptops encrypted and centrally managed?</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>2 (weak)</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>Encryption and Key Management Standard v1.1</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>(whole document)</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>encryption-standard.docx</t>
+        </is>
+      </c>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>Encryption and Key Management Standard v1.1. This standard sets the minimum encryption requirements for Quarterhour systems and data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>END-002</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr">
+        <is>
+          <t>Is anti-malware or endpoint detection software installed on company devices?</t>
+        </is>
+      </c>
+      <c r="C219" s="3" t="inlineStr">
+        <is>
+          <t>1 (weak)</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>Encryption and Key Management Standard v1.1</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>6. Laptops</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>encryption-standard.docx</t>
+        </is>
+      </c>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>Company laptops must have full-disk encryption (FileVault) turned on. This is checked through the company's device management (MDM) tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>END-005</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr">
+        <is>
+          <t>Are screen locks and automatic security updates enforced on company devices?</t>
+        </is>
+      </c>
+      <c r="C220" s="3" t="inlineStr">
+        <is>
+          <t>1 (weak)</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>Encryption and Key Management Standard v1.1</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>6. Laptops</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>encryption-standard.docx</t>
+        </is>
+      </c>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>Company laptops must have full-disk encryption (FileVault) turned on. This is checked through the company's device management (MDM) tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
           <t>PHY-002</t>
         </is>
       </c>
-      <c r="B213" s="3" t="inlineStr">
+      <c r="B221" s="3" t="inlineStr">
         <is>
           <t>Does the company have offices where customer data is accessed?</t>
         </is>
       </c>
-      <c r="C213" s="3" t="inlineStr">
+      <c r="C221" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>Business Continuity and Disaster Recovery Plan v1.0</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>6. People and workplace (page 2)</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>business-continuity-plan.pdf</t>
+        </is>
+      </c>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>Quarterhour is a remote-first company with no office. Staff can work from any location with internet access, so the loss of a workplace does not stop operations. At least two people can perform each critical task.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>PHY-002</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr">
+        <is>
+          <t>Does the company have offices where customer data is accessed?</t>
+        </is>
+      </c>
+      <c r="C222" s="3" t="inlineStr">
         <is>
           <t>2 (weak)</t>
         </is>
       </c>
-      <c r="D213" s="3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E213" s="3" t="inlineStr">
+      <c r="D222" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
         <is>
           <t>Access Control Policy v1.3</t>
         </is>
       </c>
-      <c r="F213" s="3" t="inlineStr">
+      <c r="F222" s="3" t="inlineStr">
         <is>
           <t>8. Remote access</t>
         </is>
       </c>
-      <c r="G213" s="3" t="inlineStr">
+      <c r="G222" s="3" t="inlineStr">
         <is>
           <t>access-control-policy.md</t>
         </is>
       </c>
-      <c r="H213" s="3" t="inlineStr">
+      <c r="H222" s="3" t="inlineStr">
         <is>
           <t>Quarterhour does not operate a corporate office network or VPN. Production servers are not reachable over SSH from the internet. Engineers connect through AWS Systems Manager Session Manager using their individual, MFA-protected identities.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H213"/>
+  <autoFilter ref="A1:H222"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/kits/security-questionnaire/samples/library/answer_library_DRAFT.xlsx
+++ b/kits/security-questionnaire/samples/library/answer_library_DRAFT.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>1. Answers are statements the client makes to its customers. Write only what the client's documents or written confirmations say. Never invent a control, a date, a number or a certification.</t>
+          <t>1. Answers are statements the client makes to its customers. Write only what the client's documents or written answers say. Never invent a control, a date, a number or a certification.</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2. Every answer cites its source (document and section, or a dated written confirmation). If the documents are silent, leave the answer blank and set Status to NEEDS CLIENT INPUT.</t>
+          <t>2. Every answer cites its source (document and section, or the client's dated written answers). If the documents are silent, leave the answer blank and set Status to NEEDS CLIENT INPUT.</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>The client document the answer comes from (title and version), or 'Written confirmation from &lt;name&gt;, &lt;date&gt;'.</t>
+          <t>The client document the answer comes from (title and version), or 'Written answers from &lt;name&gt;, &lt;date&gt;'.</t>
         </is>
       </c>
     </row>
